--- a/data/a_Eingangsdaten/Wärme/Warmwasserbedarf_täglich_23.xlsx
+++ b/data/a_Eingangsdaten/Wärme/Warmwasserbedarf_täglich_23.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/a_Eingangsdaten/Wärme/Warmwasserbedarf_täglich_23.xlsx
+++ b/data/a_Eingangsdaten/Wärme/Warmwasserbedarf_täglich_23.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:C366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,13 +440,21 @@
           <t>Warmwasserbedarf [GWh]</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Warmwasserbedarf [MWh]</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B2" t="n">
-        <v>240.4624668905852</v>
+        <v>291.5607411048346</v>
+      </c>
+      <c r="C2" t="n">
+        <v>291560.7411048345</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +462,10 @@
         <v>44928</v>
       </c>
       <c r="B3" t="n">
-        <v>240.5493596111166</v>
+        <v>291.6660985284789</v>
+      </c>
+      <c r="C3" t="n">
+        <v>291666.0985284789</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +473,10 @@
         <v>44929</v>
       </c>
       <c r="B4" t="n">
-        <v>240.6299195609187</v>
+        <v>291.7637774676139</v>
+      </c>
+      <c r="C4" t="n">
+        <v>291763.7774676139</v>
       </c>
     </row>
     <row r="5">
@@ -470,7 +484,10 @@
         <v>44930</v>
       </c>
       <c r="B5" t="n">
-        <v>240.7041228683397</v>
+        <v>291.8537489778619</v>
+      </c>
+      <c r="C5" t="n">
+        <v>291853.7489778619</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +495,10 @@
         <v>44931</v>
       </c>
       <c r="B6" t="n">
-        <v>240.7719475453383</v>
+        <v>291.9359863987227</v>
+      </c>
+      <c r="C6" t="n">
+        <v>291935.9863987227</v>
       </c>
     </row>
     <row r="7">
@@ -486,7 +506,10 @@
         <v>44932</v>
       </c>
       <c r="B7" t="n">
-        <v>240.8333734939988</v>
+        <v>292.0104653614736</v>
+      </c>
+      <c r="C7" t="n">
+        <v>292010.4653614736</v>
       </c>
     </row>
     <row r="8">
@@ -494,7 +517,10 @@
         <v>44933</v>
       </c>
       <c r="B8" t="n">
-        <v>240.8883825124871</v>
+        <v>292.0771637963906</v>
+      </c>
+      <c r="C8" t="n">
+        <v>292077.1637963905</v>
       </c>
     </row>
     <row r="9">
@@ -502,7 +528,10 @@
         <v>44934</v>
       </c>
       <c r="B9" t="n">
-        <v>240.9369583004436</v>
+        <v>292.1360619392879</v>
+      </c>
+      <c r="C9" t="n">
+        <v>292136.0619392879</v>
       </c>
     </row>
     <row r="10">
@@ -510,7 +539,10 @@
         <v>44935</v>
       </c>
       <c r="B10" t="n">
-        <v>240.9790864638142</v>
+        <v>292.1871423373747</v>
+      </c>
+      <c r="C10" t="n">
+        <v>292187.1423373747</v>
       </c>
     </row>
     <row r="11">
@@ -518,7 +550,10 @@
         <v>44936</v>
       </c>
       <c r="B11" t="n">
-        <v>241.0147545191147</v>
+        <v>292.2303898544266</v>
+      </c>
+      <c r="C11" t="n">
+        <v>292230.3898544266</v>
       </c>
     </row>
     <row r="12">
@@ -526,7 +561,10 @@
         <v>44937</v>
       </c>
       <c r="B12" t="n">
-        <v>241.0439518971306</v>
+        <v>292.2657916752709</v>
+      </c>
+      <c r="C12" t="n">
+        <v>292265.7916752709</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +572,10 @@
         <v>44938</v>
       </c>
       <c r="B13" t="n">
-        <v>241.0666699460488</v>
+        <v>292.2933373095842</v>
+      </c>
+      <c r="C13" t="n">
+        <v>292293.3373095841</v>
       </c>
     </row>
     <row r="14">
@@ -542,7 +583,10 @@
         <v>44939</v>
       </c>
       <c r="B14" t="n">
-        <v>241.0829019340209</v>
+        <v>292.3130185950004</v>
+      </c>
+      <c r="C14" t="n">
+        <v>292313.0185950004</v>
       </c>
     </row>
     <row r="15">
@@ -550,7 +594,10 @@
         <v>44940</v>
       </c>
       <c r="B15" t="n">
-        <v>241.0926430511587</v>
+        <v>292.3248296995299</v>
+      </c>
+      <c r="C15" t="n">
+        <v>292324.8296995299</v>
       </c>
     </row>
     <row r="16">
@@ -558,7 +605,10 @@
         <v>44941</v>
       </c>
       <c r="B16" t="n">
-        <v>241.0958904109589</v>
+        <v>292.3287671232877</v>
+      </c>
+      <c r="C16" t="n">
+        <v>292328.7671232877</v>
       </c>
     </row>
     <row r="17">
@@ -566,7 +616,10 @@
         <v>44942</v>
       </c>
       <c r="B17" t="n">
-        <v>241.0926430511587</v>
+        <v>292.3248296995299</v>
+      </c>
+      <c r="C17" t="n">
+        <v>292324.8296995299</v>
       </c>
     </row>
     <row r="18">
@@ -574,7 +627,10 @@
         <v>44943</v>
       </c>
       <c r="B18" t="n">
-        <v>241.0829019340209</v>
+        <v>292.3130185950004</v>
+      </c>
+      <c r="C18" t="n">
+        <v>292313.0185950004</v>
       </c>
     </row>
     <row r="19">
@@ -582,7 +638,10 @@
         <v>44944</v>
       </c>
       <c r="B19" t="n">
-        <v>241.0666699460488</v>
+        <v>292.2933373095842</v>
+      </c>
+      <c r="C19" t="n">
+        <v>292293.3373095841</v>
       </c>
     </row>
     <row r="20">
@@ -590,7 +649,10 @@
         <v>44945</v>
       </c>
       <c r="B20" t="n">
-        <v>241.0439518971306</v>
+        <v>292.2657916752709</v>
+      </c>
+      <c r="C20" t="n">
+        <v>292265.7916752709</v>
       </c>
     </row>
     <row r="21">
@@ -598,7 +660,10 @@
         <v>44946</v>
       </c>
       <c r="B21" t="n">
-        <v>241.0147545191147</v>
+        <v>292.2303898544266</v>
+      </c>
+      <c r="C21" t="n">
+        <v>292230.3898544266</v>
       </c>
     </row>
     <row r="22">
@@ -606,7 +671,10 @@
         <v>44947</v>
       </c>
       <c r="B22" t="n">
-        <v>240.9790864638142</v>
+        <v>292.1871423373747</v>
+      </c>
+      <c r="C22" t="n">
+        <v>292187.1423373747</v>
       </c>
     </row>
     <row r="23">
@@ -614,7 +682,10 @@
         <v>44948</v>
       </c>
       <c r="B23" t="n">
-        <v>240.9369583004436</v>
+        <v>292.1360619392879</v>
+      </c>
+      <c r="C23" t="n">
+        <v>292136.0619392879</v>
       </c>
     </row>
     <row r="24">
@@ -622,7 +693,10 @@
         <v>44949</v>
       </c>
       <c r="B24" t="n">
-        <v>240.8883825124871</v>
+        <v>292.0771637963906</v>
+      </c>
+      <c r="C24" t="n">
+        <v>292077.1637963905</v>
       </c>
     </row>
     <row r="25">
@@ -630,7 +704,10 @@
         <v>44950</v>
       </c>
       <c r="B25" t="n">
-        <v>240.8333734939988</v>
+        <v>292.0104653614736</v>
+      </c>
+      <c r="C25" t="n">
+        <v>292010.4653614736</v>
       </c>
     </row>
     <row r="26">
@@ -638,7 +715,10 @@
         <v>44951</v>
       </c>
       <c r="B26" t="n">
-        <v>240.7719475453383</v>
+        <v>291.9359863987227</v>
+      </c>
+      <c r="C26" t="n">
+        <v>291935.9863987227</v>
       </c>
     </row>
     <row r="27">
@@ -646,7 +726,10 @@
         <v>44952</v>
       </c>
       <c r="B27" t="n">
-        <v>240.7041228683397</v>
+        <v>291.8537489778619</v>
+      </c>
+      <c r="C27" t="n">
+        <v>291853.7489778619</v>
       </c>
     </row>
     <row r="28">
@@ -654,7 +737,10 @@
         <v>44953</v>
       </c>
       <c r="B28" t="n">
-        <v>240.6299195609187</v>
+        <v>291.7637774676139</v>
+      </c>
+      <c r="C28" t="n">
+        <v>291763.7774676139</v>
       </c>
     </row>
     <row r="29">
@@ -662,7 +748,10 @@
         <v>44954</v>
       </c>
       <c r="B29" t="n">
-        <v>240.5493596111166</v>
+        <v>291.6660985284789</v>
+      </c>
+      <c r="C29" t="n">
+        <v>291666.0985284789</v>
       </c>
     </row>
     <row r="30">
@@ -670,7 +759,10 @@
         <v>44955</v>
       </c>
       <c r="B30" t="n">
-        <v>240.4624668905852</v>
+        <v>291.5607411048346</v>
+      </c>
+      <c r="C30" t="n">
+        <v>291560.7411048345</v>
       </c>
     </row>
     <row r="31">
@@ -678,7 +770,10 @@
         <v>44956</v>
       </c>
       <c r="B31" t="n">
-        <v>240.3692671475129</v>
+        <v>291.4477364163595</v>
+      </c>
+      <c r="C31" t="n">
+        <v>291447.7364163595</v>
       </c>
     </row>
     <row r="32">
@@ -686,7 +781,10 @@
         <v>44957</v>
       </c>
       <c r="B32" t="n">
-        <v>240.269787998995</v>
+        <v>291.3271179487815</v>
+      </c>
+      <c r="C32" t="n">
+        <v>291327.1179487815</v>
       </c>
     </row>
     <row r="33">
@@ -694,7 +792,10 @@
         <v>44958</v>
       </c>
       <c r="B33" t="n">
-        <v>240.1640589228502</v>
+        <v>291.1989214439558</v>
+      </c>
+      <c r="C33" t="n">
+        <v>291198.9214439559</v>
       </c>
     </row>
     <row r="34">
@@ -702,7 +803,10 @@
         <v>44959</v>
       </c>
       <c r="B34" t="n">
-        <v>240.0521112488854</v>
+        <v>291.0631848892735</v>
+      </c>
+      <c r="C34" t="n">
+        <v>291063.1848892735</v>
       </c>
     </row>
     <row r="35">
@@ -710,7 +814,10 @@
         <v>44960</v>
       </c>
       <c r="B35" t="n">
-        <v>239.9339781496126</v>
+        <v>290.9199485064053</v>
+      </c>
+      <c r="C35" t="n">
+        <v>290919.9485064053</v>
       </c>
     </row>
     <row r="36">
@@ -718,7 +825,10 @@
         <v>44961</v>
       </c>
       <c r="B36" t="n">
-        <v>239.8096946304185</v>
+        <v>290.7692547393825</v>
+      </c>
+      <c r="C36" t="n">
+        <v>290769.2547393825</v>
       </c>
     </row>
     <row r="37">
@@ -726,7 +836,10 @@
         <v>44962</v>
       </c>
       <c r="B37" t="n">
-        <v>239.6792975191923</v>
+        <v>290.6111482420206</v>
+      </c>
+      <c r="C37" t="n">
+        <v>290611.1482420206</v>
       </c>
     </row>
     <row r="38">
@@ -734,7 +847,10 @@
         <v>44963</v>
       </c>
       <c r="B38" t="n">
-        <v>239.542825455412</v>
+        <v>290.4456758646871</v>
+      </c>
+      <c r="C38" t="n">
+        <v>290445.6758646871</v>
       </c>
     </row>
     <row r="39">
@@ -742,7 +858,10 @@
         <v>44964</v>
       </c>
       <c r="B39" t="n">
-        <v>239.4003188786956</v>
+        <v>290.2728866404184</v>
+      </c>
+      <c r="C39" t="n">
+        <v>290272.8866404184</v>
       </c>
     </row>
     <row r="40">
@@ -750,7 +869,10 @@
         <v>44965</v>
       </c>
       <c r="B40" t="n">
-        <v>239.2518200168172</v>
+        <v>290.0928317703909</v>
+      </c>
+      <c r="C40" t="n">
+        <v>290092.831770391</v>
       </c>
     </row>
     <row r="41">
@@ -758,7 +880,10 @@
         <v>44966</v>
       </c>
       <c r="B41" t="n">
-        <v>239.0973728731946</v>
+        <v>289.9055646087484</v>
+      </c>
+      <c r="C41" t="n">
+        <v>289905.5646087484</v>
       </c>
     </row>
     <row r="42">
@@ -766,7 +891,10 @@
         <v>44967</v>
       </c>
       <c r="B42" t="n">
-        <v>238.9370232138495</v>
+        <v>289.7111406467926</v>
+      </c>
+      <c r="C42" t="n">
+        <v>289711.1406467925</v>
       </c>
     </row>
     <row r="43">
@@ -774,7 +902,10 @@
         <v>44968</v>
       </c>
       <c r="B43" t="n">
-        <v>238.7708185538467</v>
+        <v>289.5096174965391</v>
+      </c>
+      <c r="C43" t="n">
+        <v>289509.6174965391</v>
       </c>
     </row>
     <row r="44">
@@ -782,7 +913,10 @@
         <v>44969</v>
       </c>
       <c r="B44" t="n">
-        <v>238.598808143214</v>
+        <v>289.301054873647</v>
+      </c>
+      <c r="C44" t="n">
+        <v>289301.054873647</v>
       </c>
     </row>
     <row r="45">
@@ -790,7 +924,10 @@
         <v>44970</v>
       </c>
       <c r="B45" t="n">
-        <v>238.4210429523482</v>
+        <v>289.0855145797223</v>
+      </c>
+      <c r="C45" t="n">
+        <v>289085.5145797223</v>
       </c>
     </row>
     <row r="46">
@@ -798,7 +935,10 @@
         <v>44971</v>
       </c>
       <c r="B46" t="n">
-        <v>238.237575656912</v>
+        <v>288.8630604840059</v>
+      </c>
+      <c r="C46" t="n">
+        <v>288863.0604840059</v>
       </c>
     </row>
     <row r="47">
@@ -806,7 +946,10 @@
         <v>44972</v>
       </c>
       <c r="B47" t="n">
-        <v>238.0484606222245</v>
+        <v>288.6337585044473</v>
+      </c>
+      <c r="C47" t="n">
+        <v>288633.7585044472</v>
       </c>
     </row>
     <row r="48">
@@ -814,7 +957,10 @@
         <v>44973</v>
       </c>
       <c r="B48" t="n">
-        <v>237.853753887152</v>
+        <v>288.3976765881717</v>
+      </c>
+      <c r="C48" t="n">
+        <v>288397.6765881717</v>
       </c>
     </row>
     <row r="49">
@@ -822,7 +968,10 @@
         <v>44974</v>
       </c>
       <c r="B49" t="n">
-        <v>237.6535131475021</v>
+        <v>288.1548846913463</v>
+      </c>
+      <c r="C49" t="n">
+        <v>288154.8846913463</v>
       </c>
     </row>
     <row r="50">
@@ -830,7 +979,10 @@
         <v>44975</v>
       </c>
       <c r="B50" t="n">
-        <v>237.4477977389276</v>
+        <v>287.9054547584497</v>
+      </c>
+      <c r="C50" t="n">
+        <v>287905.4547584496</v>
       </c>
     </row>
     <row r="51">
@@ -838,7 +990,10 @@
         <v>44976</v>
       </c>
       <c r="B51" t="n">
-        <v>237.2366686193436</v>
+        <v>287.6494607009542</v>
+      </c>
+      <c r="C51" t="n">
+        <v>287649.4607009542</v>
       </c>
     </row>
     <row r="52">
@@ -846,7 +1001,10 @@
         <v>44977</v>
       </c>
       <c r="B52" t="n">
-        <v>237.0201883508651</v>
+        <v>287.3869783754239</v>
+      </c>
+      <c r="C52" t="n">
+        <v>287386.9783754239</v>
       </c>
     </row>
     <row r="53">
@@ -854,7 +1012,10 @@
         <v>44978</v>
       </c>
       <c r="B53" t="n">
-        <v>236.7984210812673</v>
+        <v>287.1180855610367</v>
+      </c>
+      <c r="C53" t="n">
+        <v>287118.0855610367</v>
       </c>
     </row>
     <row r="54">
@@ -862,7 +1023,10 @@
         <v>44979</v>
       </c>
       <c r="B54" t="n">
-        <v>236.5714325249786</v>
+        <v>286.8428619365366</v>
+      </c>
+      <c r="C54" t="n">
+        <v>286842.8619365366</v>
       </c>
     </row>
     <row r="55">
@@ -870,7 +1034,10 @@
         <v>44980</v>
       </c>
       <c r="B55" t="n">
-        <v>236.3392899436068</v>
+        <v>286.5613890566233</v>
+      </c>
+      <c r="C55" t="n">
+        <v>286561.3890566233</v>
       </c>
     </row>
     <row r="56">
@@ -878,7 +1045,10 @@
         <v>44981</v>
       </c>
       <c r="B56" t="n">
-        <v>236.1020621260091</v>
+        <v>286.273750327786</v>
+      </c>
+      <c r="C56" t="n">
+        <v>286273.750327786</v>
       </c>
     </row>
     <row r="57">
@@ -886,7 +1056,10 @@
         <v>44982</v>
       </c>
       <c r="B57" t="n">
-        <v>235.8598193679074</v>
+        <v>285.9800309835877</v>
+      </c>
+      <c r="C57" t="n">
+        <v>285980.0309835877</v>
       </c>
     </row>
     <row r="58">
@@ -894,7 +1067,10 @@
         <v>44983</v>
       </c>
       <c r="B58" t="n">
-        <v>235.6126334510591</v>
+        <v>285.6803180594091</v>
+      </c>
+      <c r="C58" t="n">
+        <v>285680.3180594091</v>
       </c>
     </row>
     <row r="59">
@@ -902,7 +1078,10 @@
         <v>44984</v>
       </c>
       <c r="B59" t="n">
-        <v>235.3605776219859</v>
+        <v>285.3747003666579</v>
+      </c>
+      <c r="C59" t="n">
+        <v>285374.7003666579</v>
       </c>
     </row>
     <row r="60">
@@ -910,7 +1089,10 @@
         <v>44985</v>
       </c>
       <c r="B60" t="n">
-        <v>235.1037265702699</v>
+        <v>285.0632684664523</v>
+      </c>
+      <c r="C60" t="n">
+        <v>285063.2684664523</v>
       </c>
     </row>
     <row r="61">
@@ -918,7 +1100,10 @@
         <v>44986</v>
       </c>
       <c r="B61" t="n">
-        <v>234.8421564064211</v>
+        <v>284.7461146427855</v>
+      </c>
+      <c r="C61" t="n">
+        <v>284746.1146427855</v>
       </c>
     </row>
     <row r="62">
@@ -926,7 +1111,10 @@
         <v>44987</v>
       </c>
       <c r="B62" t="n">
-        <v>234.575944639324</v>
+        <v>284.4233328751803</v>
+      </c>
+      <c r="C62" t="n">
+        <v>284423.3328751803</v>
       </c>
     </row>
     <row r="63">
@@ -934,7 +1122,10 @@
         <v>44988</v>
       </c>
       <c r="B63" t="n">
-        <v>234.3051701532706</v>
+        <v>284.0950188108406</v>
+      </c>
+      <c r="C63" t="n">
+        <v>284095.0188108406</v>
       </c>
     </row>
     <row r="64">
@@ -942,7 +1133,10 @@
         <v>44989</v>
       </c>
       <c r="B64" t="n">
-        <v>234.029913184585</v>
+        <v>283.7612697363093</v>
+      </c>
+      <c r="C64" t="n">
+        <v>283761.2697363093</v>
       </c>
     </row>
     <row r="65">
@@ -950,7 +1144,10 @@
         <v>44990</v>
       </c>
       <c r="B65" t="n">
-        <v>233.7502552978474</v>
+        <v>283.4221845486399</v>
+      </c>
+      <c r="C65" t="n">
+        <v>283422.1845486399</v>
       </c>
     </row>
     <row r="66">
@@ -958,7 +1155,10 @@
         <v>44991</v>
       </c>
       <c r="B66" t="n">
-        <v>233.4662793617252</v>
+        <v>283.0778637260918</v>
+      </c>
+      <c r="C66" t="n">
+        <v>283077.8637260919</v>
       </c>
     </row>
     <row r="67">
@@ -966,7 +1166,10 @@
         <v>44992</v>
       </c>
       <c r="B67" t="n">
-        <v>233.1780695244171</v>
+        <v>282.7284092983557</v>
+      </c>
+      <c r="C67" t="n">
+        <v>282728.4092983557</v>
       </c>
     </row>
     <row r="68">
@@ -974,7 +1177,10 @@
         <v>44993</v>
       </c>
       <c r="B68" t="n">
-        <v>232.8857111887177</v>
+        <v>282.3739248163203</v>
+      </c>
+      <c r="C68" t="n">
+        <v>282373.9248163202</v>
       </c>
     </row>
     <row r="69">
@@ -982,7 +1188,10 @@
         <v>44994</v>
       </c>
       <c r="B69" t="n">
-        <v>232.5892909867117</v>
+        <v>282.014515321388</v>
+      </c>
+      <c r="C69" t="n">
+        <v>282014.515321388</v>
       </c>
     </row>
     <row r="70">
@@ -990,7 +1199,10 @@
         <v>44995</v>
       </c>
       <c r="B70" t="n">
-        <v>232.2888967541023</v>
+        <v>281.650287314349</v>
+      </c>
+      <c r="C70" t="n">
+        <v>281650.287314349</v>
       </c>
     </row>
     <row r="71">
@@ -998,7 +1210,10 @@
         <v>44996</v>
       </c>
       <c r="B71" t="n">
-        <v>231.9846175041834</v>
+        <v>281.2813487238224</v>
+      </c>
+      <c r="C71" t="n">
+        <v>281281.3487238224</v>
       </c>
     </row>
     <row r="72">
@@ -1006,7 +1221,10 @@
         <v>44997</v>
       </c>
       <c r="B72" t="n">
-        <v>231.6765434014638</v>
+        <v>280.9078088742749</v>
+      </c>
+      <c r="C72" t="n">
+        <v>280907.8088742749</v>
       </c>
     </row>
     <row r="73">
@@ -1014,7 +1232,10 @@
         <v>44998</v>
       </c>
       <c r="B73" t="n">
-        <v>231.3647657349489</v>
+        <v>280.5297784536256</v>
+      </c>
+      <c r="C73" t="n">
+        <v>280529.7784536256</v>
       </c>
     </row>
     <row r="74">
@@ -1022,7 +1243,10 @@
         <v>44999</v>
       </c>
       <c r="B74" t="n">
-        <v>231.04937689109</v>
+        <v>280.1473694804466</v>
+      </c>
+      <c r="C74" t="n">
+        <v>280147.3694804466</v>
       </c>
     </row>
     <row r="75">
@@ -1030,7 +1254,10 @@
         <v>45000</v>
       </c>
       <c r="B75" t="n">
-        <v>230.7304703264082</v>
+        <v>279.7606952707699</v>
+      </c>
+      <c r="C75" t="n">
+        <v>279760.6952707699</v>
       </c>
     </row>
     <row r="76">
@@ -1038,7 +1265,10 @@
         <v>45001</v>
       </c>
       <c r="B76" t="n">
-        <v>230.4081405398011</v>
+        <v>279.3698704045088</v>
+      </c>
+      <c r="C76" t="n">
+        <v>279369.8704045088</v>
       </c>
     </row>
     <row r="77">
@@ -1046,7 +1276,10 @@
         <v>45002</v>
       </c>
       <c r="B77" t="n">
-        <v>230.0824830445409</v>
+        <v>278.9750106915059</v>
+      </c>
+      <c r="C77" t="n">
+        <v>278975.0106915059</v>
       </c>
     </row>
     <row r="78">
@@ -1054,7 +1287,10 @@
         <v>45003</v>
       </c>
       <c r="B78" t="n">
-        <v>229.7535943399719</v>
+        <v>278.5762331372159</v>
+      </c>
+      <c r="C78" t="n">
+        <v>278576.2331372159</v>
       </c>
     </row>
     <row r="79">
@@ -1062,7 +1298,10 @@
         <v>45004</v>
       </c>
       <c r="B79" t="n">
-        <v>229.4215718829151</v>
+        <v>278.1736559080346</v>
+      </c>
+      <c r="C79" t="n">
+        <v>278173.6559080346</v>
       </c>
     </row>
     <row r="80">
@@ -1070,7 +1309,10 @@
         <v>45005</v>
       </c>
       <c r="B80" t="n">
-        <v>229.0865140587902</v>
+        <v>277.7673982962831</v>
+      </c>
+      <c r="C80" t="n">
+        <v>277767.3982962832</v>
       </c>
     </row>
     <row r="81">
@@ -1078,7 +1320,10 @@
         <v>45006</v>
       </c>
       <c r="B81" t="n">
-        <v>228.7485201524617</v>
+        <v>277.3575806848598</v>
+      </c>
+      <c r="C81" t="n">
+        <v>277357.5806848598</v>
       </c>
     </row>
     <row r="82">
@@ -1086,7 +1331,10 @@
         <v>45007</v>
       </c>
       <c r="B82" t="n">
-        <v>228.4076903188184</v>
+        <v>276.9443245115673</v>
+      </c>
+      <c r="C82" t="n">
+        <v>276944.3245115674</v>
       </c>
     </row>
     <row r="83">
@@ -1094,7 +1342,10 @@
         <v>45008</v>
       </c>
       <c r="B83" t="n">
-        <v>228.0641255530958</v>
+        <v>276.5277522331288</v>
+      </c>
+      <c r="C83" t="n">
+        <v>276527.7522331288</v>
       </c>
     </row>
     <row r="84">
@@ -1102,7 +1353,10 @@
         <v>45009</v>
       </c>
       <c r="B84" t="n">
-        <v>227.7179276609488</v>
+        <v>276.1079872889004</v>
+      </c>
+      <c r="C84" t="n">
+        <v>276107.9872889004</v>
       </c>
     </row>
     <row r="85">
@@ -1110,7 +1364,10 @@
         <v>45010</v>
       </c>
       <c r="B85" t="n">
-        <v>227.3691992282842</v>
+        <v>275.6851540642946</v>
+      </c>
+      <c r="C85" t="n">
+        <v>275685.1540642946</v>
       </c>
     </row>
     <row r="86">
@@ -1118,7 +1375,10 @@
         <v>45011</v>
       </c>
       <c r="B86" t="n">
-        <v>227.018043590863</v>
+        <v>275.2593778539214</v>
+      </c>
+      <c r="C86" t="n">
+        <v>275259.3778539214</v>
       </c>
     </row>
     <row r="87">
@@ -1126,7 +1386,10 @@
         <v>45012</v>
       </c>
       <c r="B87" t="n">
-        <v>226.664564803679</v>
+        <v>274.8307848244609</v>
+      </c>
+      <c r="C87" t="n">
+        <v>274830.7848244609</v>
       </c>
     </row>
     <row r="88">
@@ -1134,7 +1397,10 @@
         <v>45013</v>
       </c>
       <c r="B88" t="n">
-        <v>226.3088676101256</v>
+        <v>274.3995019772773</v>
+      </c>
+      <c r="C88" t="n">
+        <v>274399.5019772773</v>
       </c>
     </row>
     <row r="89">
@@ -1142,7 +1408,10 @@
         <v>45014</v>
       </c>
       <c r="B89" t="n">
-        <v>225.9510574109577</v>
+        <v>273.9656571107863</v>
+      </c>
+      <c r="C89" t="n">
+        <v>273965.6571107862</v>
       </c>
     </row>
     <row r="90">
@@ -1150,7 +1419,10 @@
         <v>45015</v>
       </c>
       <c r="B90" t="n">
-        <v>225.5912402330597</v>
+        <v>273.5293787825849</v>
+      </c>
+      <c r="C90" t="n">
+        <v>273529.3787825849</v>
       </c>
     </row>
     <row r="91">
@@ -1158,7 +1430,10 @@
         <v>45016</v>
       </c>
       <c r="B91" t="n">
-        <v>225.2295226980267</v>
+        <v>273.0907962713574</v>
+      </c>
+      <c r="C91" t="n">
+        <v>273090.7962713573</v>
       </c>
     </row>
     <row r="92">
@@ -1166,7 +1441,10 @@
         <v>45017</v>
       </c>
       <c r="B92" t="n">
-        <v>224.866011990571</v>
+        <v>272.6500395385673</v>
+      </c>
+      <c r="C92" t="n">
+        <v>272650.0395385673</v>
       </c>
     </row>
     <row r="93">
@@ -1174,7 +1452,10 @@
         <v>45018</v>
       </c>
       <c r="B93" t="n">
-        <v>224.5008158267602</v>
+        <v>272.2072391899468</v>
+      </c>
+      <c r="C93" t="n">
+        <v>272207.2391899468</v>
       </c>
     </row>
     <row r="94">
@@ -1182,7 +1463,10 @@
         <v>45019</v>
       </c>
       <c r="B94" t="n">
-        <v>224.1340424220995</v>
+        <v>271.7625264367956</v>
+      </c>
+      <c r="C94" t="n">
+        <v>271762.5264367956</v>
       </c>
     </row>
     <row r="95">
@@ -1190,7 +1474,10 @@
         <v>45020</v>
       </c>
       <c r="B95" t="n">
-        <v>223.7658004594641</v>
+        <v>271.3160330571002</v>
+      </c>
+      <c r="C95" t="n">
+        <v>271316.0330571002</v>
       </c>
     </row>
     <row r="96">
@@ -1198,7 +1485,10 @@
         <v>45021</v>
       </c>
       <c r="B96" t="n">
-        <v>223.3961990568949</v>
+        <v>270.8678913564851</v>
+      </c>
+      <c r="C96" t="n">
+        <v>270867.8913564851</v>
       </c>
     </row>
     <row r="97">
@@ -1206,7 +1496,10 @@
         <v>45022</v>
       </c>
       <c r="B97" t="n">
-        <v>223.0253477352642</v>
+        <v>270.4182341290078</v>
+      </c>
+      <c r="C97" t="n">
+        <v>270418.2341290078</v>
       </c>
     </row>
     <row r="98">
@@ -1214,7 +1507,10 @@
         <v>45023</v>
       </c>
       <c r="B98" t="n">
-        <v>222.6533563858221</v>
+        <v>269.9671946178093</v>
+      </c>
+      <c r="C98" t="n">
+        <v>269967.1946178093</v>
       </c>
     </row>
     <row r="99">
@@ -1222,7 +1518,10 @@
         <v>45024</v>
       </c>
       <c r="B99" t="n">
-        <v>222.2803352376338</v>
+        <v>269.514906475631</v>
+      </c>
+      <c r="C99" t="n">
+        <v>269514.906475631</v>
       </c>
     </row>
     <row r="100">
@@ -1230,7 +1529,10 @@
         <v>45025</v>
       </c>
       <c r="B100" t="n">
-        <v>221.9063948249159</v>
+        <v>269.0615037252106</v>
+      </c>
+      <c r="C100" t="n">
+        <v>269061.5037252106</v>
       </c>
     </row>
     <row r="101">
@@ -1238,7 +1540,10 @@
         <v>45026</v>
       </c>
       <c r="B101" t="n">
-        <v>221.5316459542831</v>
+        <v>268.6071207195682</v>
+      </c>
+      <c r="C101" t="n">
+        <v>268607.1207195682</v>
       </c>
     </row>
     <row r="102">
@@ -1246,7 +1551,10 @@
         <v>45027</v>
       </c>
       <c r="B102" t="n">
-        <v>221.1561996719132</v>
+        <v>268.1518921021948</v>
+      </c>
+      <c r="C102" t="n">
+        <v>268151.8921021948</v>
       </c>
     </row>
     <row r="103">
@@ -1254,7 +1562,10 @@
         <v>45028</v>
       </c>
       <c r="B103" t="n">
-        <v>220.7801672306428</v>
+        <v>267.6959527671544</v>
+      </c>
+      <c r="C103" t="n">
+        <v>267695.9527671544</v>
       </c>
     </row>
     <row r="104">
@@ -1262,7 +1573,10 @@
         <v>45029</v>
       </c>
       <c r="B104" t="n">
-        <v>220.4036600569995</v>
+        <v>267.239437819112</v>
+      </c>
+      <c r="C104" t="n">
+        <v>267239.437819112</v>
       </c>
     </row>
     <row r="105">
@@ -1270,7 +1584,10 @@
         <v>45030</v>
       </c>
       <c r="B105" t="n">
-        <v>220.0267897181846</v>
+        <v>266.7824825332989</v>
+      </c>
+      <c r="C105" t="n">
+        <v>266782.4825332989</v>
       </c>
     </row>
     <row r="106">
@@ -1278,7 +1595,10 @@
         <v>45031</v>
       </c>
       <c r="B106" t="n">
-        <v>219.6496678890131</v>
+        <v>266.3252223154284</v>
+      </c>
+      <c r="C106" t="n">
+        <v>266325.2223154284</v>
       </c>
     </row>
     <row r="107">
@@ -1286,7 +1606,10 @@
         <v>45032</v>
       </c>
       <c r="B107" t="n">
-        <v>219.2724063188218</v>
+        <v>265.8677926615714</v>
+      </c>
+      <c r="C107" t="n">
+        <v>265867.7926615714</v>
       </c>
     </row>
     <row r="108">
@@ -1294,7 +1617,10 @@
         <v>45033</v>
       </c>
       <c r="B108" t="n">
-        <v>218.895116798356</v>
+        <v>265.4103291180066</v>
+      </c>
+      <c r="C108" t="n">
+        <v>265410.3291180066</v>
       </c>
     </row>
     <row r="109">
@@ -1302,7 +1628,10 @@
         <v>45034</v>
       </c>
       <c r="B109" t="n">
-        <v>218.5179111266431</v>
+        <v>264.9529672410548</v>
+      </c>
+      <c r="C109" t="n">
+        <v>264952.9672410548</v>
       </c>
     </row>
     <row r="110">
@@ -1310,7 +1639,10 @@
         <v>45035</v>
       </c>
       <c r="B110" t="n">
-        <v>218.1409010778645</v>
+        <v>264.4958425569107</v>
+      </c>
+      <c r="C110" t="n">
+        <v>264495.8425569107</v>
       </c>
     </row>
     <row r="111">
@@ -1318,7 +1650,10 @@
         <v>45036</v>
       </c>
       <c r="B111" t="n">
-        <v>217.7641983682342</v>
+        <v>264.0390905214839</v>
+      </c>
+      <c r="C111" t="n">
+        <v>264039.0905214839</v>
       </c>
     </row>
     <row r="112">
@@ -1326,7 +1661,10 @@
         <v>45037</v>
       </c>
       <c r="B112" t="n">
-        <v>217.3879146228948</v>
+        <v>263.58284648026</v>
+      </c>
+      <c r="C112" t="n">
+        <v>263582.84648026</v>
       </c>
     </row>
     <row r="113">
@@ -1334,7 +1672,10 @@
         <v>45038</v>
       </c>
       <c r="B113" t="n">
-        <v>217.0121613428412</v>
+        <v>263.1272456281949</v>
+      </c>
+      <c r="C113" t="n">
+        <v>263127.2456281949</v>
       </c>
     </row>
     <row r="114">
@@ -1342,7 +1683,10 @@
         <v>45039</v>
       </c>
       <c r="B114" t="n">
-        <v>216.6370498718794</v>
+        <v>262.6724229696538</v>
+      </c>
+      <c r="C114" t="n">
+        <v>262672.4229696539</v>
       </c>
     </row>
     <row r="115">
@@ -1350,7 +1694,10 @@
         <v>45040</v>
       </c>
       <c r="B115" t="n">
-        <v>216.262691363634</v>
+        <v>262.2185132784063</v>
+      </c>
+      <c r="C115" t="n">
+        <v>262218.5132784063</v>
       </c>
     </row>
     <row r="116">
@@ -1358,7 +1705,10 @@
         <v>45041</v>
       </c>
       <c r="B116" t="n">
-        <v>215.8891967486103</v>
+        <v>261.76565105769</v>
+      </c>
+      <c r="C116" t="n">
+        <v>261765.65105769</v>
       </c>
     </row>
     <row r="117">
@@ -1366,7 +1716,10 @@
         <v>45042</v>
       </c>
       <c r="B117" t="n">
-        <v>215.5166767013234</v>
+        <v>261.3139705003546</v>
+      </c>
+      <c r="C117" t="n">
+        <v>261313.9705003546</v>
       </c>
     </row>
     <row r="118">
@@ -1374,7 +1727,10 @@
         <v>45043</v>
       </c>
       <c r="B118" t="n">
-        <v>215.1452416075029</v>
+        <v>260.8636054490973</v>
+      </c>
+      <c r="C118" t="n">
+        <v>260863.6054490973</v>
       </c>
     </row>
     <row r="119">
@@ -1382,7 +1738,10 @@
         <v>45044</v>
       </c>
       <c r="B119" t="n">
-        <v>214.7750015313833</v>
+        <v>260.4146893568023</v>
+      </c>
+      <c r="C119" t="n">
+        <v>260414.6893568023</v>
       </c>
     </row>
     <row r="120">
@@ -1390,7 +1749,10 @@
         <v>45045</v>
       </c>
       <c r="B120" t="n">
-        <v>214.4060661830897</v>
+        <v>259.9673552469963</v>
+      </c>
+      <c r="C120" t="n">
+        <v>259967.3552469963</v>
       </c>
     </row>
     <row r="121">
@@ -1398,7 +1760,10 @@
         <v>45046</v>
       </c>
       <c r="B121" t="n">
-        <v>214.038544886128</v>
+        <v>259.5217356744302</v>
+      </c>
+      <c r="C121" t="n">
+        <v>259521.7356744302</v>
       </c>
     </row>
     <row r="122">
@@ -1406,7 +1771,10 @@
         <v>45047</v>
       </c>
       <c r="B122" t="n">
-        <v>213.6725465449902</v>
+        <v>259.0779626858007</v>
+      </c>
+      <c r="C122" t="n">
+        <v>259077.9626858007</v>
       </c>
     </row>
     <row r="123">
@@ -1414,7 +1782,10 @@
         <v>45048</v>
       </c>
       <c r="B123" t="n">
-        <v>213.3081796128839</v>
+        <v>258.6361677806217</v>
+      </c>
+      <c r="C123" t="n">
+        <v>258636.1677806217</v>
       </c>
     </row>
     <row r="124">
@@ -1422,7 +1793,10 @@
         <v>45049</v>
       </c>
       <c r="B124" t="n">
-        <v>212.9455520595944</v>
+        <v>258.1964818722583</v>
+      </c>
+      <c r="C124" t="n">
+        <v>258196.4818722583</v>
       </c>
     </row>
     <row r="125">
@@ -1430,7 +1804,10 @@
         <v>45050</v>
       </c>
       <c r="B125" t="n">
-        <v>212.5847713394922</v>
+        <v>257.7590352491343</v>
+      </c>
+      <c r="C125" t="n">
+        <v>257759.0352491344</v>
       </c>
     </row>
     <row r="126">
@@ -1438,7 +1815,10 @@
         <v>45051</v>
       </c>
       <c r="B126" t="n">
-        <v>212.2259443596908</v>
+        <v>257.3239575361251</v>
+      </c>
+      <c r="C126" t="n">
+        <v>257323.9575361251</v>
       </c>
     </row>
     <row r="127">
@@ -1446,7 +1826,10 @@
         <v>45052</v>
       </c>
       <c r="B127" t="n">
-        <v>211.8691774483685</v>
+        <v>256.8913776561468</v>
+      </c>
+      <c r="C127" t="n">
+        <v>256891.3776561468</v>
       </c>
     </row>
     <row r="128">
@@ -1454,7 +1837,10 @@
         <v>45053</v>
       </c>
       <c r="B128" t="n">
-        <v>211.5145763232607</v>
+        <v>256.4614237919537</v>
+      </c>
+      <c r="C128" t="n">
+        <v>256461.4237919537</v>
       </c>
     </row>
     <row r="129">
@@ -1462,7 +1848,10 @@
         <v>45054</v>
       </c>
       <c r="B129" t="n">
-        <v>211.1622460603338</v>
+        <v>256.0342233481547</v>
+      </c>
+      <c r="C129" t="n">
+        <v>256034.2233481547</v>
       </c>
     </row>
     <row r="130">
@@ -1470,7 +1859,10 @@
         <v>45055</v>
       </c>
       <c r="B130" t="n">
-        <v>210.8122910626486</v>
+        <v>255.6099029134614</v>
+      </c>
+      <c r="C130" t="n">
+        <v>255609.9029134614</v>
       </c>
     </row>
     <row r="131">
@@ -1478,7 +1870,10 @@
         <v>45056</v>
       </c>
       <c r="B131" t="n">
-        <v>210.4648150294234</v>
+        <v>255.1885882231759</v>
+      </c>
+      <c r="C131" t="n">
+        <v>255188.5882231759</v>
       </c>
     </row>
     <row r="132">
@@ -1486,7 +1881,10 @@
         <v>45057</v>
       </c>
       <c r="B132" t="n">
-        <v>210.1199209253062</v>
+        <v>254.7704041219338</v>
+      </c>
+      <c r="C132" t="n">
+        <v>254770.4041219338</v>
       </c>
     </row>
     <row r="133">
@@ -1494,7 +1892,10 @@
         <v>45058</v>
       </c>
       <c r="B133" t="n">
-        <v>209.7777109498634</v>
+        <v>254.3554745267093</v>
+      </c>
+      <c r="C133" t="n">
+        <v>254355.4745267094</v>
       </c>
     </row>
     <row r="134">
@@ -1502,7 +1903,10 @@
         <v>45059</v>
       </c>
       <c r="B134" t="n">
-        <v>209.4382865072961</v>
+        <v>253.9439223900966</v>
+      </c>
+      <c r="C134" t="n">
+        <v>253943.9223900966</v>
       </c>
     </row>
     <row r="135">
@@ -1510,7 +1914,10 @@
         <v>45060</v>
       </c>
       <c r="B135" t="n">
-        <v>209.1017481763922</v>
+        <v>253.5358696638756</v>
+      </c>
+      <c r="C135" t="n">
+        <v>253535.8696638756</v>
       </c>
     </row>
     <row r="136">
@@ -1518,7 +1925,10 @@
         <v>45061</v>
       </c>
       <c r="B136" t="n">
-        <v>208.7681956807222</v>
+        <v>253.1314372628757</v>
+      </c>
+      <c r="C136" t="n">
+        <v>253131.4372628757</v>
       </c>
     </row>
     <row r="137">
@@ -1526,7 +1936,10 @@
         <v>45062</v>
       </c>
       <c r="B137" t="n">
-        <v>208.4377278590891</v>
+        <v>252.7307450291456</v>
+      </c>
+      <c r="C137" t="n">
+        <v>252730.7450291456</v>
       </c>
     </row>
     <row r="138">
@@ -1534,7 +1947,10 @@
         <v>45063</v>
       </c>
       <c r="B138" t="n">
-        <v>208.1104426362407</v>
+        <v>252.3339116964418</v>
+      </c>
+      <c r="C138" t="n">
+        <v>252333.9116964418</v>
       </c>
     </row>
     <row r="139">
@@ -1542,7 +1958,10 @@
         <v>45064</v>
       </c>
       <c r="B139" t="n">
-        <v>207.7864369938517</v>
+        <v>251.9410548550452</v>
+      </c>
+      <c r="C139" t="n">
+        <v>251941.0548550452</v>
       </c>
     </row>
     <row r="140">
@@ -1550,7 +1969,10 @@
         <v>45065</v>
       </c>
       <c r="B140" t="n">
-        <v>207.4658069417868</v>
+        <v>251.5522909169165</v>
+      </c>
+      <c r="C140" t="n">
+        <v>251552.2909169164</v>
       </c>
     </row>
     <row r="141">
@@ -1558,7 +1980,10 @@
         <v>45066</v>
       </c>
       <c r="B141" t="n">
-        <v>207.14864748965</v>
+        <v>251.1677350812006</v>
+      </c>
+      <c r="C141" t="n">
+        <v>251167.7350812006</v>
       </c>
     </row>
     <row r="142">
@@ -1566,7 +1991,10 @@
         <v>45067</v>
       </c>
       <c r="B142" t="n">
-        <v>206.8350526186319</v>
+        <v>250.7875013000912</v>
+      </c>
+      <c r="C142" t="n">
+        <v>250787.5013000912</v>
       </c>
     </row>
     <row r="143">
@@ -1574,7 +2002,10 @@
         <v>45068</v>
       </c>
       <c r="B143" t="n">
-        <v>206.5251152536608</v>
+        <v>250.4117022450637</v>
+      </c>
+      <c r="C143" t="n">
+        <v>250411.7022450637</v>
       </c>
     </row>
     <row r="144">
@@ -1582,7 +2013,10 @@
         <v>45069</v>
       </c>
       <c r="B144" t="n">
-        <v>206.2189272358668</v>
+        <v>250.0404492734885</v>
+      </c>
+      <c r="C144" t="n">
+        <v>250040.4492734885</v>
       </c>
     </row>
     <row r="145">
@@ -1590,7 +2024,10 @@
         <v>45070</v>
       </c>
       <c r="B145" t="n">
-        <v>205.9165792953677</v>
+        <v>249.6738523956334</v>
+      </c>
+      <c r="C145" t="n">
+        <v>249673.8523956334</v>
       </c>
     </row>
     <row r="146">
@@ -1598,7 +2035,10 @@
         <v>45071</v>
       </c>
       <c r="B146" t="n">
-        <v>205.6181610243835</v>
+        <v>249.312020242065</v>
+      </c>
+      <c r="C146" t="n">
+        <v>249312.020242065</v>
       </c>
     </row>
     <row r="147">
@@ -1606,7 +2046,10 @@
         <v>45072</v>
       </c>
       <c r="B147" t="n">
-        <v>205.3237608506882</v>
+        <v>248.9550600314595</v>
+      </c>
+      <c r="C147" t="n">
+        <v>248955.0600314595</v>
       </c>
     </row>
     <row r="148">
@@ -1614,7 +2057,10 @@
         <v>45073</v>
       </c>
       <c r="B148" t="n">
-        <v>205.0334660114071</v>
+        <v>248.6030775388311</v>
+      </c>
+      <c r="C148" t="n">
+        <v>248603.0775388311</v>
       </c>
     </row>
     <row r="149">
@@ -1622,7 +2068,10 @@
         <v>45074</v>
       </c>
       <c r="B149" t="n">
-        <v>204.747362527166</v>
+        <v>248.2561770641888</v>
+      </c>
+      <c r="C149" t="n">
+        <v>248256.1770641888</v>
       </c>
     </row>
     <row r="150">
@@ -1630,7 +2079,10 @@
         <v>45075</v>
       </c>
       <c r="B150" t="n">
-        <v>204.465535176602</v>
+        <v>247.91446140163</v>
+      </c>
+      <c r="C150" t="n">
+        <v>247914.46140163</v>
       </c>
     </row>
     <row r="151">
@@ -1638,7 +2090,10 @@
         <v>45076</v>
       </c>
       <c r="B151" t="n">
-        <v>204.1880674712414</v>
+        <v>247.5780318088802</v>
+      </c>
+      <c r="C151" t="n">
+        <v>247578.0318088802</v>
       </c>
     </row>
     <row r="152">
@@ -1646,7 +2101,10 @@
         <v>45077</v>
       </c>
       <c r="B152" t="n">
-        <v>203.9150416307535</v>
+        <v>247.2469879772886</v>
+      </c>
+      <c r="C152" t="n">
+        <v>247246.9879772886</v>
       </c>
     </row>
     <row r="153">
@@ -1654,7 +2112,10 @@
         <v>45078</v>
       </c>
       <c r="B153" t="n">
-        <v>203.6465385585872</v>
+        <v>246.921428002287</v>
+      </c>
+      <c r="C153" t="n">
+        <v>246921.428002287</v>
       </c>
     </row>
     <row r="154">
@@ -1662,7 +2123,10 @@
         <v>45079</v>
       </c>
       <c r="B154" t="n">
-        <v>203.3826378179976</v>
+        <v>246.6014483543221</v>
+      </c>
+      <c r="C154" t="n">
+        <v>246601.4483543221</v>
       </c>
     </row>
     <row r="155">
@@ -1670,7 +2134,10 @@
         <v>45080</v>
       </c>
       <c r="B155" t="n">
-        <v>203.1234176084695</v>
+        <v>246.2871438502693</v>
+      </c>
+      <c r="C155" t="n">
+        <v>246287.1438502693</v>
       </c>
     </row>
     <row r="156">
@@ -1678,7 +2145,10 @@
         <v>45081</v>
       </c>
       <c r="B156" t="n">
-        <v>202.8689547425455</v>
+        <v>245.9786076253364</v>
+      </c>
+      <c r="C156" t="n">
+        <v>245978.6076253364</v>
       </c>
     </row>
     <row r="157">
@@ -1686,7 +2156,10 @@
         <v>45082</v>
       </c>
       <c r="B157" t="n">
-        <v>202.6193246230645</v>
+        <v>245.6759311054658</v>
+      </c>
+      <c r="C157" t="n">
+        <v>245675.9311054658</v>
       </c>
     </row>
     <row r="158">
@@ -1694,7 +2167,10 @@
         <v>45083</v>
       </c>
       <c r="B158" t="n">
-        <v>202.3746012208184</v>
+        <v>245.3792039802424</v>
+      </c>
+      <c r="C158" t="n">
+        <v>245379.2039802423</v>
       </c>
     </row>
     <row r="159">
@@ -1702,7 +2178,10 @@
         <v>45084</v>
       </c>
       <c r="B159" t="n">
-        <v>202.1348570526328</v>
+        <v>245.0885141763173</v>
+      </c>
+      <c r="C159" t="n">
+        <v>245088.5141763173</v>
       </c>
     </row>
     <row r="160">
@@ -1710,7 +2189,10 @@
         <v>45085</v>
       </c>
       <c r="B160" t="n">
-        <v>201.9001631598789</v>
+        <v>244.8039478313532</v>
+      </c>
+      <c r="C160" t="n">
+        <v>244803.9478313532</v>
       </c>
     </row>
     <row r="161">
@@ -1718,7 +2200,10 @@
         <v>45086</v>
       </c>
       <c r="B161" t="n">
-        <v>201.6705890874221</v>
+        <v>244.5255892684993</v>
+      </c>
+      <c r="C161" t="n">
+        <v>244525.5892684993</v>
       </c>
     </row>
     <row r="162">
@@ -1726,7 +2211,10 @@
         <v>45087</v>
       </c>
       <c r="B162" t="n">
-        <v>201.4462028630149</v>
+        <v>244.2535209714055</v>
+      </c>
+      <c r="C162" t="n">
+        <v>244253.5209714055</v>
       </c>
     </row>
     <row r="163">
@@ -1734,7 +2222,10 @@
         <v>45088</v>
       </c>
       <c r="B163" t="n">
-        <v>201.227070977138</v>
+        <v>243.9878235597798</v>
+      </c>
+      <c r="C163" t="n">
+        <v>243987.8235597798</v>
       </c>
     </row>
     <row r="164">
@@ -1742,7 +2233,10 @@
         <v>45089</v>
       </c>
       <c r="B164" t="n">
-        <v>201.0132583632985</v>
+        <v>243.7285757654995</v>
+      </c>
+      <c r="C164" t="n">
+        <v>243728.5757654995</v>
       </c>
     </row>
     <row r="165">
@@ -1750,7 +2244,10 @@
         <v>45090</v>
       </c>
       <c r="B165" t="n">
-        <v>200.8048283787885</v>
+        <v>243.4758544092811</v>
+      </c>
+      <c r="C165" t="n">
+        <v>243475.854409281</v>
       </c>
     </row>
     <row r="166">
@@ -1758,7 +2255,10 @@
         <v>45091</v>
       </c>
       <c r="B166" t="n">
-        <v>200.6018427859105</v>
+        <v>243.2297343779165</v>
+      </c>
+      <c r="C166" t="n">
+        <v>243229.7343779166</v>
       </c>
     </row>
     <row r="167">
@@ -1766,7 +2266,10 @@
         <v>45092</v>
       </c>
       <c r="B167" t="n">
-        <v>200.4043617336766</v>
+        <v>242.9902886020829</v>
+      </c>
+      <c r="C167" t="n">
+        <v>242990.2886020829</v>
       </c>
     </row>
     <row r="168">
@@ -1774,7 +2277,10 @@
         <v>45093</v>
       </c>
       <c r="B168" t="n">
-        <v>200.2124437399845</v>
+        <v>242.7575880347312</v>
+      </c>
+      <c r="C168" t="n">
+        <v>242757.5880347312</v>
       </c>
     </row>
     <row r="169">
@@ -1782,7 +2288,10 @@
         <v>45094</v>
       </c>
       <c r="B169" t="n">
-        <v>200.0261456742777</v>
+        <v>242.5317016300617</v>
+      </c>
+      <c r="C169" t="n">
+        <v>242531.7016300617</v>
       </c>
     </row>
     <row r="170">
@@ -1790,7 +2299,10 @@
         <v>45095</v>
       </c>
       <c r="B170" t="n">
-        <v>199.8455227406936</v>
+        <v>242.312696323091</v>
+      </c>
+      <c r="C170" t="n">
+        <v>242312.696323091</v>
       </c>
     </row>
     <row r="171">
@@ -1798,7 +2310,10 @@
         <v>45096</v>
       </c>
       <c r="B171" t="n">
-        <v>199.6706284617057</v>
+        <v>242.1006370098182</v>
+      </c>
+      <c r="C171" t="n">
+        <v>242100.6370098182</v>
       </c>
     </row>
     <row r="172">
@@ -1806,7 +2321,10 @@
         <v>45097</v>
       </c>
       <c r="B172" t="n">
-        <v>199.5015146622634</v>
+        <v>241.8955865279943</v>
+      </c>
+      <c r="C172" t="n">
+        <v>241895.5865279943</v>
       </c>
     </row>
     <row r="173">
@@ -1814,7 +2332,10 @@
         <v>45098</v>
       </c>
       <c r="B173" t="n">
-        <v>199.3382314544351</v>
+        <v>241.6976056385026</v>
+      </c>
+      <c r="C173" t="n">
+        <v>241697.6056385026</v>
       </c>
     </row>
     <row r="174">
@@ -1822,7 +2343,10 @@
         <v>45099</v>
       </c>
       <c r="B174" t="n">
-        <v>199.1808272225594</v>
+        <v>241.5067530073533</v>
+      </c>
+      <c r="C174" t="n">
+        <v>241506.7530073533</v>
       </c>
     </row>
     <row r="175">
@@ -1830,7 +2354,10 @@
         <v>45100</v>
       </c>
       <c r="B175" t="n">
-        <v>199.0293486089072</v>
+        <v>241.3230851883</v>
+      </c>
+      <c r="C175" t="n">
+        <v>241323.0851882999</v>
       </c>
     </row>
     <row r="176">
@@ -1838,7 +2365,10 @@
         <v>45101</v>
       </c>
       <c r="B176" t="n">
-        <v>198.8838404998608</v>
+        <v>241.1466566060813</v>
+      </c>
+      <c r="C176" t="n">
+        <v>241146.6566060813</v>
       </c>
     </row>
     <row r="177">
@@ -1846,7 +2376,10 @@
         <v>45102</v>
       </c>
       <c r="B177" t="n">
-        <v>198.7443460126134</v>
+        <v>240.9775195402938</v>
+      </c>
+      <c r="C177" t="n">
+        <v>240977.5195402938</v>
       </c>
     </row>
     <row r="178">
@@ -1854,7 +2387,10 @@
         <v>45103</v>
       </c>
       <c r="B178" t="n">
-        <v>198.610906482392</v>
+        <v>240.8157241099003</v>
+      </c>
+      <c r="C178" t="n">
+        <v>240815.7241099003</v>
       </c>
     </row>
     <row r="179">
@@ -1862,7 +2398,10 @@
         <v>45104</v>
       </c>
       <c r="B179" t="n">
-        <v>198.4835614502093</v>
+        <v>240.6613182583788</v>
+      </c>
+      <c r="C179" t="n">
+        <v>240661.3182583788</v>
       </c>
     </row>
     <row r="180">
@@ -1870,7 +2409,10 @@
         <v>45105</v>
       </c>
       <c r="B180" t="n">
-        <v>198.3623486511467</v>
+        <v>240.5143477395154</v>
+      </c>
+      <c r="C180" t="n">
+        <v>240514.3477395154</v>
       </c>
     </row>
     <row r="181">
@@ -1878,7 +2420,10 @@
         <v>45106</v>
       </c>
       <c r="B181" t="n">
-        <v>198.2473040031725</v>
+        <v>240.3748561038466</v>
+      </c>
+      <c r="C181" t="n">
+        <v>240374.8561038466</v>
       </c>
     </row>
     <row r="182">
@@ -1886,7 +2431,10 @@
         <v>45107</v>
       </c>
       <c r="B182" t="n">
-        <v>198.1384615964987</v>
+        <v>240.2428846857547</v>
+      </c>
+      <c r="C182" t="n">
+        <v>240242.8846857547</v>
       </c>
     </row>
     <row r="183">
@@ -1894,7 +2442,10 @@
         <v>45108</v>
       </c>
       <c r="B183" t="n">
-        <v>198.0358536834796</v>
+        <v>240.118472591219</v>
+      </c>
+      <c r="C183" t="n">
+        <v>240118.472591219</v>
       </c>
     </row>
     <row r="184">
@@ -1902,7 +2453,10 @@
         <v>45109</v>
       </c>
       <c r="B184" t="n">
-        <v>197.9395106690541</v>
+        <v>240.0016566862281</v>
+      </c>
+      <c r="C184" t="n">
+        <v>240001.6566862281</v>
       </c>
     </row>
     <row r="185">
@@ -1910,7 +2464,10 @@
         <v>45110</v>
       </c>
       <c r="B185" t="n">
-        <v>197.8494611017367</v>
+        <v>239.8924715858558</v>
+      </c>
+      <c r="C185" t="n">
+        <v>239892.4715858558</v>
       </c>
     </row>
     <row r="186">
@@ -1918,7 +2475,10 @@
         <v>45111</v>
       </c>
       <c r="B186" t="n">
-        <v>197.7657316651577</v>
+        <v>239.7909496440037</v>
+      </c>
+      <c r="C186" t="n">
+        <v>239790.9496440037</v>
       </c>
     </row>
     <row r="187">
@@ -1926,7 +2486,10 @@
         <v>45112</v>
       </c>
       <c r="B187" t="n">
-        <v>197.688347170156</v>
+        <v>239.6971209438142</v>
+      </c>
+      <c r="C187" t="n">
+        <v>239697.1209438142</v>
       </c>
     </row>
     <row r="188">
@@ -1934,7 +2497,10 @@
         <v>45113</v>
       </c>
       <c r="B188" t="n">
-        <v>197.6173305474277</v>
+        <v>239.6110132887561</v>
+      </c>
+      <c r="C188" t="n">
+        <v>239611.0132887561</v>
       </c>
     </row>
     <row r="189">
@@ -1942,7 +2508,10 @@
         <v>45114</v>
       </c>
       <c r="B189" t="n">
-        <v>197.5527028407308</v>
+        <v>239.5326521943861</v>
+      </c>
+      <c r="C189" t="n">
+        <v>239532.6521943861</v>
       </c>
     </row>
     <row r="190">
@@ -1950,7 +2519,10 @@
         <v>45115</v>
       </c>
       <c r="B190" t="n">
-        <v>197.4944832006495</v>
+        <v>239.4620608807875</v>
+      </c>
+      <c r="C190" t="n">
+        <v>239462.0608807875</v>
       </c>
     </row>
     <row r="191">
@@ -1958,7 +2530,10 @@
         <v>45116</v>
       </c>
       <c r="B191" t="n">
-        <v>197.4426888789197</v>
+        <v>239.3992602656901</v>
+      </c>
+      <c r="C191" t="n">
+        <v>239399.2602656901</v>
       </c>
     </row>
     <row r="192">
@@ -1966,7 +2541,10 @@
         <v>45117</v>
       </c>
       <c r="B192" t="n">
-        <v>197.3973352233166</v>
+        <v>239.3442689582714</v>
+      </c>
+      <c r="C192" t="n">
+        <v>239344.2689582715</v>
       </c>
     </row>
     <row r="193">
@@ -1974,7 +2552,10 @@
         <v>45118</v>
       </c>
       <c r="B193" t="n">
-        <v>197.3584356731074</v>
+        <v>239.2971032536427</v>
+      </c>
+      <c r="C193" t="n">
+        <v>239297.1032536427</v>
       </c>
     </row>
     <row r="194">
@@ -1982,7 +2563,10 @@
         <v>45119</v>
       </c>
       <c r="B194" t="n">
-        <v>197.3260017550682</v>
+        <v>239.2577771280202</v>
+      </c>
+      <c r="C194" t="n">
+        <v>239257.7771280202</v>
       </c>
     </row>
     <row r="195">
@@ -1990,7 +2574,10 @@
         <v>45120</v>
       </c>
       <c r="B195" t="n">
-        <v>197.3000430800689</v>
+        <v>239.2263022345835</v>
+      </c>
+      <c r="C195" t="n">
+        <v>239226.3022345835</v>
       </c>
     </row>
     <row r="196">
@@ -1998,7 +2585,10 @@
         <v>45121</v>
       </c>
       <c r="B196" t="n">
-        <v>197.2805673402251</v>
+        <v>239.2026879000229</v>
+      </c>
+      <c r="C196" t="n">
+        <v>239202.6879000229</v>
       </c>
     </row>
     <row r="197">
@@ -2006,7 +2596,10 @@
         <v>45122</v>
       </c>
       <c r="B197" t="n">
-        <v>197.2675803066189</v>
+        <v>239.1869411217755</v>
+      </c>
+      <c r="C197" t="n">
+        <v>239186.9411217755</v>
       </c>
     </row>
     <row r="198">
@@ -2014,7 +2607,10 @@
         <v>45123</v>
       </c>
       <c r="B198" t="n">
-        <v>197.2610858275887</v>
+        <v>239.1790665659513</v>
+      </c>
+      <c r="C198" t="n">
+        <v>239179.0665659513</v>
       </c>
     </row>
     <row r="199">
@@ -2022,7 +2618,10 @@
         <v>45124</v>
       </c>
       <c r="B199" t="n">
-        <v>197.2610858275887</v>
+        <v>239.1790665659513</v>
+      </c>
+      <c r="C199" t="n">
+        <v>239179.0665659513</v>
       </c>
     </row>
     <row r="200">
@@ -2030,7 +2629,10 @@
         <v>45125</v>
       </c>
       <c r="B200" t="n">
-        <v>197.2675803066189</v>
+        <v>239.1869411217755</v>
+      </c>
+      <c r="C200" t="n">
+        <v>239186.9411217755</v>
       </c>
     </row>
     <row r="201">
@@ -2038,7 +2640,10 @@
         <v>45126</v>
       </c>
       <c r="B201" t="n">
-        <v>197.2805673402251</v>
+        <v>239.2026879000229</v>
+      </c>
+      <c r="C201" t="n">
+        <v>239202.6879000229</v>
       </c>
     </row>
     <row r="202">
@@ -2046,7 +2651,10 @@
         <v>45127</v>
       </c>
       <c r="B202" t="n">
-        <v>197.3000430800689</v>
+        <v>239.2263022345835</v>
+      </c>
+      <c r="C202" t="n">
+        <v>239226.3022345835</v>
       </c>
     </row>
     <row r="203">
@@ -2054,7 +2662,10 @@
         <v>45128</v>
       </c>
       <c r="B203" t="n">
-        <v>197.3260017550682</v>
+        <v>239.2577771280202</v>
+      </c>
+      <c r="C203" t="n">
+        <v>239257.7771280202</v>
       </c>
     </row>
     <row r="204">
@@ -2062,7 +2673,10 @@
         <v>45129</v>
       </c>
       <c r="B204" t="n">
-        <v>197.3584356731074</v>
+        <v>239.2971032536427</v>
+      </c>
+      <c r="C204" t="n">
+        <v>239297.1032536427</v>
       </c>
     </row>
     <row r="205">
@@ -2070,7 +2684,10 @@
         <v>45130</v>
       </c>
       <c r="B205" t="n">
-        <v>197.3973352233166</v>
+        <v>239.3442689582714</v>
+      </c>
+      <c r="C205" t="n">
+        <v>239344.2689582715</v>
       </c>
     </row>
     <row r="206">
@@ -2078,7 +2695,10 @@
         <v>45131</v>
       </c>
       <c r="B206" t="n">
-        <v>197.4426888789197</v>
+        <v>239.3992602656901</v>
+      </c>
+      <c r="C206" t="n">
+        <v>239399.2602656901</v>
       </c>
     </row>
     <row r="207">
@@ -2086,7 +2706,10 @@
         <v>45132</v>
       </c>
       <c r="B207" t="n">
-        <v>197.4944832006495</v>
+        <v>239.4620608807875</v>
+      </c>
+      <c r="C207" t="n">
+        <v>239462.0608807875</v>
       </c>
     </row>
     <row r="208">
@@ -2094,7 +2717,10 @@
         <v>45133</v>
       </c>
       <c r="B208" t="n">
-        <v>197.5527028407308</v>
+        <v>239.5326521943861</v>
+      </c>
+      <c r="C208" t="n">
+        <v>239532.6521943861</v>
       </c>
     </row>
     <row r="209">
@@ -2102,7 +2728,10 @@
         <v>45134</v>
       </c>
       <c r="B209" t="n">
-        <v>197.6173305474277</v>
+        <v>239.6110132887561</v>
+      </c>
+      <c r="C209" t="n">
+        <v>239611.0132887561</v>
       </c>
     </row>
     <row r="210">
@@ -2110,7 +2739,10 @@
         <v>45135</v>
       </c>
       <c r="B210" t="n">
-        <v>197.688347170156</v>
+        <v>239.6971209438142</v>
+      </c>
+      <c r="C210" t="n">
+        <v>239697.1209438142</v>
       </c>
     </row>
     <row r="211">
@@ -2118,7 +2750,10 @@
         <v>45136</v>
       </c>
       <c r="B211" t="n">
-        <v>197.7657316651577</v>
+        <v>239.7909496440037</v>
+      </c>
+      <c r="C211" t="n">
+        <v>239790.9496440037</v>
       </c>
     </row>
     <row r="212">
@@ -2126,7 +2761,10 @@
         <v>45137</v>
       </c>
       <c r="B212" t="n">
-        <v>197.8494611017367</v>
+        <v>239.8924715858558</v>
+      </c>
+      <c r="C212" t="n">
+        <v>239892.4715858558</v>
       </c>
     </row>
     <row r="213">
@@ -2134,7 +2772,10 @@
         <v>45138</v>
       </c>
       <c r="B213" t="n">
-        <v>197.9395106690541</v>
+        <v>240.0016566862281</v>
+      </c>
+      <c r="C213" t="n">
+        <v>240001.6566862281</v>
       </c>
     </row>
     <row r="214">
@@ -2142,7 +2783,10 @@
         <v>45139</v>
       </c>
       <c r="B214" t="n">
-        <v>198.0358536834796</v>
+        <v>240.118472591219</v>
+      </c>
+      <c r="C214" t="n">
+        <v>240118.472591219</v>
       </c>
     </row>
     <row r="215">
@@ -2150,7 +2794,10 @@
         <v>45140</v>
       </c>
       <c r="B215" t="n">
-        <v>198.1384615964987</v>
+        <v>240.2428846857547</v>
+      </c>
+      <c r="C215" t="n">
+        <v>240242.8846857547</v>
       </c>
     </row>
     <row r="216">
@@ -2158,7 +2805,10 @@
         <v>45141</v>
       </c>
       <c r="B216" t="n">
-        <v>198.2473040031725</v>
+        <v>240.3748561038466</v>
+      </c>
+      <c r="C216" t="n">
+        <v>240374.8561038466</v>
       </c>
     </row>
     <row r="217">
@@ -2166,7 +2816,10 @@
         <v>45142</v>
       </c>
       <c r="B217" t="n">
-        <v>198.3623486511467</v>
+        <v>240.5143477395154</v>
+      </c>
+      <c r="C217" t="n">
+        <v>240514.3477395154</v>
       </c>
     </row>
     <row r="218">
@@ -2174,7 +2827,10 @@
         <v>45143</v>
       </c>
       <c r="B218" t="n">
-        <v>198.4835614502093</v>
+        <v>240.6613182583788</v>
+      </c>
+      <c r="C218" t="n">
+        <v>240661.3182583788</v>
       </c>
     </row>
     <row r="219">
@@ -2182,7 +2838,10 @@
         <v>45144</v>
       </c>
       <c r="B219" t="n">
-        <v>198.610906482392</v>
+        <v>240.8157241099003</v>
+      </c>
+      <c r="C219" t="n">
+        <v>240815.7241099003</v>
       </c>
     </row>
     <row r="220">
@@ -2190,7 +2849,10 @@
         <v>45145</v>
       </c>
       <c r="B220" t="n">
-        <v>198.7443460126134</v>
+        <v>240.9775195402938</v>
+      </c>
+      <c r="C220" t="n">
+        <v>240977.5195402938</v>
       </c>
     </row>
     <row r="221">
@@ -2198,7 +2860,10 @@
         <v>45146</v>
       </c>
       <c r="B221" t="n">
-        <v>198.8838404998608</v>
+        <v>241.1466566060813</v>
+      </c>
+      <c r="C221" t="n">
+        <v>241146.6566060813</v>
       </c>
     </row>
     <row r="222">
@@ -2206,7 +2871,10 @@
         <v>45147</v>
       </c>
       <c r="B222" t="n">
-        <v>199.0293486089072</v>
+        <v>241.3230851883</v>
+      </c>
+      <c r="C222" t="n">
+        <v>241323.0851882999</v>
       </c>
     </row>
     <row r="223">
@@ -2214,7 +2882,10 @@
         <v>45148</v>
       </c>
       <c r="B223" t="n">
-        <v>199.1808272225594</v>
+        <v>241.5067530073533</v>
+      </c>
+      <c r="C223" t="n">
+        <v>241506.7530073533</v>
       </c>
     </row>
     <row r="224">
@@ -2222,7 +2893,10 @@
         <v>45149</v>
       </c>
       <c r="B224" t="n">
-        <v>199.3382314544351</v>
+        <v>241.6976056385026</v>
+      </c>
+      <c r="C224" t="n">
+        <v>241697.6056385026</v>
       </c>
     </row>
     <row r="225">
@@ -2230,7 +2904,10 @@
         <v>45150</v>
       </c>
       <c r="B225" t="n">
-        <v>199.5015146622634</v>
+        <v>241.8955865279943</v>
+      </c>
+      <c r="C225" t="n">
+        <v>241895.5865279943</v>
       </c>
     </row>
     <row r="226">
@@ -2238,7 +2915,10 @@
         <v>45151</v>
       </c>
       <c r="B226" t="n">
-        <v>199.6706284617057</v>
+        <v>242.1006370098182</v>
+      </c>
+      <c r="C226" t="n">
+        <v>242100.6370098182</v>
       </c>
     </row>
     <row r="227">
@@ -2246,7 +2926,10 @@
         <v>45152</v>
       </c>
       <c r="B227" t="n">
-        <v>199.8455227406936</v>
+        <v>242.312696323091</v>
+      </c>
+      <c r="C227" t="n">
+        <v>242312.696323091</v>
       </c>
     </row>
     <row r="228">
@@ -2254,7 +2937,10 @@
         <v>45153</v>
       </c>
       <c r="B228" t="n">
-        <v>200.0261456742777</v>
+        <v>242.5317016300617</v>
+      </c>
+      <c r="C228" t="n">
+        <v>242531.7016300617</v>
       </c>
     </row>
     <row r="229">
@@ -2262,7 +2948,10 @@
         <v>45154</v>
       </c>
       <c r="B229" t="n">
-        <v>200.2124437399845</v>
+        <v>242.7575880347312</v>
+      </c>
+      <c r="C229" t="n">
+        <v>242757.5880347312</v>
       </c>
     </row>
     <row r="230">
@@ -2270,7 +2959,10 @@
         <v>45155</v>
       </c>
       <c r="B230" t="n">
-        <v>200.4043617336766</v>
+        <v>242.9902886020829</v>
+      </c>
+      <c r="C230" t="n">
+        <v>242990.2886020829</v>
       </c>
     </row>
     <row r="231">
@@ -2278,7 +2970,10 @@
         <v>45156</v>
       </c>
       <c r="B231" t="n">
-        <v>200.6018427859105</v>
+        <v>243.2297343779165</v>
+      </c>
+      <c r="C231" t="n">
+        <v>243229.7343779166</v>
       </c>
     </row>
     <row r="232">
@@ -2286,7 +2981,10 @@
         <v>45157</v>
       </c>
       <c r="B232" t="n">
-        <v>200.8048283787885</v>
+        <v>243.4758544092811</v>
+      </c>
+      <c r="C232" t="n">
+        <v>243475.854409281</v>
       </c>
     </row>
     <row r="233">
@@ -2294,7 +2992,10 @@
         <v>45158</v>
       </c>
       <c r="B233" t="n">
-        <v>201.0132583632985</v>
+        <v>243.7285757654995</v>
+      </c>
+      <c r="C233" t="n">
+        <v>243728.5757654995</v>
       </c>
     </row>
     <row r="234">
@@ -2302,7 +3003,10 @@
         <v>45159</v>
       </c>
       <c r="B234" t="n">
-        <v>201.227070977138</v>
+        <v>243.9878235597798</v>
+      </c>
+      <c r="C234" t="n">
+        <v>243987.8235597798</v>
       </c>
     </row>
     <row r="235">
@@ -2310,7 +3014,10 @@
         <v>45160</v>
       </c>
       <c r="B235" t="n">
-        <v>201.4462028630149</v>
+        <v>244.2535209714055</v>
+      </c>
+      <c r="C235" t="n">
+        <v>244253.5209714055</v>
       </c>
     </row>
     <row r="236">
@@ -2318,7 +3025,10 @@
         <v>45161</v>
       </c>
       <c r="B236" t="n">
-        <v>201.6705890874221</v>
+        <v>244.5255892684993</v>
+      </c>
+      <c r="C236" t="n">
+        <v>244525.5892684993</v>
       </c>
     </row>
     <row r="237">
@@ -2326,7 +3036,10 @@
         <v>45162</v>
       </c>
       <c r="B237" t="n">
-        <v>201.9001631598789</v>
+        <v>244.8039478313532</v>
+      </c>
+      <c r="C237" t="n">
+        <v>244803.9478313532</v>
       </c>
     </row>
     <row r="238">
@@ -2334,7 +3047,10 @@
         <v>45163</v>
       </c>
       <c r="B238" t="n">
-        <v>202.1348570526328</v>
+        <v>245.0885141763173</v>
+      </c>
+      <c r="C238" t="n">
+        <v>245088.5141763173</v>
       </c>
     </row>
     <row r="239">
@@ -2342,7 +3058,10 @@
         <v>45164</v>
       </c>
       <c r="B239" t="n">
-        <v>202.3746012208184</v>
+        <v>245.3792039802424</v>
+      </c>
+      <c r="C239" t="n">
+        <v>245379.2039802423</v>
       </c>
     </row>
     <row r="240">
@@ -2350,7 +3069,10 @@
         <v>45165</v>
       </c>
       <c r="B240" t="n">
-        <v>202.6193246230645</v>
+        <v>245.6759311054658</v>
+      </c>
+      <c r="C240" t="n">
+        <v>245675.9311054658</v>
       </c>
     </row>
     <row r="241">
@@ -2358,7 +3080,10 @@
         <v>45166</v>
       </c>
       <c r="B241" t="n">
-        <v>202.8689547425455</v>
+        <v>245.9786076253364</v>
+      </c>
+      <c r="C241" t="n">
+        <v>245978.6076253364</v>
       </c>
     </row>
     <row r="242">
@@ -2366,7 +3091,10 @@
         <v>45167</v>
       </c>
       <c r="B242" t="n">
-        <v>203.1234176084695</v>
+        <v>246.2871438502693</v>
+      </c>
+      <c r="C242" t="n">
+        <v>246287.1438502693</v>
       </c>
     </row>
     <row r="243">
@@ -2374,7 +3102,10 @@
         <v>45168</v>
       </c>
       <c r="B243" t="n">
-        <v>203.3826378179975</v>
+        <v>246.601448354322</v>
+      </c>
+      <c r="C243" t="n">
+        <v>246601.448354322</v>
       </c>
     </row>
     <row r="244">
@@ -2382,7 +3113,10 @@
         <v>45169</v>
       </c>
       <c r="B244" t="n">
-        <v>203.6465385585872</v>
+        <v>246.9214280022869</v>
+      </c>
+      <c r="C244" t="n">
+        <v>246921.4280022869</v>
       </c>
     </row>
     <row r="245">
@@ -2390,7 +3124,10 @@
         <v>45170</v>
       </c>
       <c r="B245" t="n">
-        <v>203.9150416307534</v>
+        <v>247.2469879772886</v>
+      </c>
+      <c r="C245" t="n">
+        <v>247246.9879772886</v>
       </c>
     </row>
     <row r="246">
@@ -2398,7 +3135,10 @@
         <v>45171</v>
       </c>
       <c r="B246" t="n">
-        <v>204.1880674712414</v>
+        <v>247.5780318088802</v>
+      </c>
+      <c r="C246" t="n">
+        <v>247578.0318088802</v>
       </c>
     </row>
     <row r="247">
@@ -2406,7 +3146,10 @@
         <v>45172</v>
       </c>
       <c r="B247" t="n">
-        <v>204.465535176602</v>
+        <v>247.91446140163</v>
+      </c>
+      <c r="C247" t="n">
+        <v>247914.46140163</v>
       </c>
     </row>
     <row r="248">
@@ -2414,7 +3157,10 @@
         <v>45173</v>
       </c>
       <c r="B248" t="n">
-        <v>204.747362527166</v>
+        <v>248.2561770641888</v>
+      </c>
+      <c r="C248" t="n">
+        <v>248256.1770641888</v>
       </c>
     </row>
     <row r="249">
@@ -2422,7 +3168,10 @@
         <v>45174</v>
       </c>
       <c r="B249" t="n">
-        <v>205.0334660114071</v>
+        <v>248.6030775388311</v>
+      </c>
+      <c r="C249" t="n">
+        <v>248603.0775388311</v>
       </c>
     </row>
     <row r="250">
@@ -2430,7 +3179,10 @@
         <v>45175</v>
       </c>
       <c r="B250" t="n">
-        <v>205.3237608506882</v>
+        <v>248.9550600314595</v>
+      </c>
+      <c r="C250" t="n">
+        <v>248955.0600314595</v>
       </c>
     </row>
     <row r="251">
@@ -2438,7 +3190,10 @@
         <v>45176</v>
       </c>
       <c r="B251" t="n">
-        <v>205.6181610243835</v>
+        <v>249.312020242065</v>
+      </c>
+      <c r="C251" t="n">
+        <v>249312.020242065</v>
       </c>
     </row>
     <row r="252">
@@ -2446,7 +3201,10 @@
         <v>45177</v>
       </c>
       <c r="B252" t="n">
-        <v>205.9165792953677</v>
+        <v>249.6738523956333</v>
+      </c>
+      <c r="C252" t="n">
+        <v>249673.8523956333</v>
       </c>
     </row>
     <row r="253">
@@ -2454,7 +3212,10 @@
         <v>45178</v>
       </c>
       <c r="B253" t="n">
-        <v>206.2189272358668</v>
+        <v>250.0404492734885</v>
+      </c>
+      <c r="C253" t="n">
+        <v>250040.4492734885</v>
       </c>
     </row>
     <row r="254">
@@ -2462,7 +3223,10 @@
         <v>45179</v>
       </c>
       <c r="B254" t="n">
-        <v>206.5251152536608</v>
+        <v>250.4117022450637</v>
+      </c>
+      <c r="C254" t="n">
+        <v>250411.7022450637</v>
       </c>
     </row>
     <row r="255">
@@ -2470,7 +3234,10 @@
         <v>45180</v>
       </c>
       <c r="B255" t="n">
-        <v>206.8350526186319</v>
+        <v>250.7875013000912</v>
+      </c>
+      <c r="C255" t="n">
+        <v>250787.5013000912</v>
       </c>
     </row>
     <row r="256">
@@ -2478,7 +3245,10 @@
         <v>45181</v>
       </c>
       <c r="B256" t="n">
-        <v>207.14864748965</v>
+        <v>251.1677350812006</v>
+      </c>
+      <c r="C256" t="n">
+        <v>251167.7350812006</v>
       </c>
     </row>
     <row r="257">
@@ -2486,7 +3256,10 @@
         <v>45182</v>
       </c>
       <c r="B257" t="n">
-        <v>207.4658069417868</v>
+        <v>251.5522909169165</v>
+      </c>
+      <c r="C257" t="n">
+        <v>251552.2909169164</v>
       </c>
     </row>
     <row r="258">
@@ -2494,7 +3267,10 @@
         <v>45183</v>
       </c>
       <c r="B258" t="n">
-        <v>207.7864369938517</v>
+        <v>251.9410548550452</v>
+      </c>
+      <c r="C258" t="n">
+        <v>251941.0548550452</v>
       </c>
     </row>
     <row r="259">
@@ -2502,7 +3278,10 @@
         <v>45184</v>
       </c>
       <c r="B259" t="n">
-        <v>208.1104426362407</v>
+        <v>252.3339116964418</v>
+      </c>
+      <c r="C259" t="n">
+        <v>252333.9116964418</v>
       </c>
     </row>
     <row r="260">
@@ -2510,7 +3289,10 @@
         <v>45185</v>
       </c>
       <c r="B260" t="n">
-        <v>208.4377278590891</v>
+        <v>252.7307450291455</v>
+      </c>
+      <c r="C260" t="n">
+        <v>252730.7450291455</v>
       </c>
     </row>
     <row r="261">
@@ -2518,7 +3300,10 @@
         <v>45186</v>
       </c>
       <c r="B261" t="n">
-        <v>208.7681956807222</v>
+        <v>253.1314372628757</v>
+      </c>
+      <c r="C261" t="n">
+        <v>253131.4372628757</v>
       </c>
     </row>
     <row r="262">
@@ -2526,7 +3311,10 @@
         <v>45187</v>
       </c>
       <c r="B262" t="n">
-        <v>209.1017481763922</v>
+        <v>253.5358696638756</v>
+      </c>
+      <c r="C262" t="n">
+        <v>253535.8696638756</v>
       </c>
     </row>
     <row r="263">
@@ -2534,7 +3322,10 @@
         <v>45188</v>
       </c>
       <c r="B263" t="n">
-        <v>209.4382865072961</v>
+        <v>253.9439223900966</v>
+      </c>
+      <c r="C263" t="n">
+        <v>253943.9223900966</v>
       </c>
     </row>
     <row r="264">
@@ -2542,7 +3333,10 @@
         <v>45189</v>
       </c>
       <c r="B264" t="n">
-        <v>209.7777109498633</v>
+        <v>254.3554745267093</v>
+      </c>
+      <c r="C264" t="n">
+        <v>254355.4745267093</v>
       </c>
     </row>
     <row r="265">
@@ -2550,7 +3344,10 @@
         <v>45190</v>
       </c>
       <c r="B265" t="n">
-        <v>210.1199209253062</v>
+        <v>254.7704041219338</v>
+      </c>
+      <c r="C265" t="n">
+        <v>254770.4041219338</v>
       </c>
     </row>
     <row r="266">
@@ -2558,7 +3355,10 @@
         <v>45191</v>
       </c>
       <c r="B266" t="n">
-        <v>210.4648150294234</v>
+        <v>255.1885882231759</v>
+      </c>
+      <c r="C266" t="n">
+        <v>255188.5882231759</v>
       </c>
     </row>
     <row r="267">
@@ -2566,7 +3366,10 @@
         <v>45192</v>
       </c>
       <c r="B267" t="n">
-        <v>210.8122910626486</v>
+        <v>255.6099029134614</v>
+      </c>
+      <c r="C267" t="n">
+        <v>255609.9029134614</v>
       </c>
     </row>
     <row r="268">
@@ -2574,7 +3377,10 @@
         <v>45193</v>
       </c>
       <c r="B268" t="n">
-        <v>211.1622460603338</v>
+        <v>256.0342233481547</v>
+      </c>
+      <c r="C268" t="n">
+        <v>256034.2233481547</v>
       </c>
     </row>
     <row r="269">
@@ -2582,7 +3388,10 @@
         <v>45194</v>
       </c>
       <c r="B269" t="n">
-        <v>211.5145763232607</v>
+        <v>256.4614237919537</v>
+      </c>
+      <c r="C269" t="n">
+        <v>256461.4237919537</v>
       </c>
     </row>
     <row r="270">
@@ -2590,7 +3399,10 @@
         <v>45195</v>
       </c>
       <c r="B270" t="n">
-        <v>211.8691774483685</v>
+        <v>256.8913776561468</v>
+      </c>
+      <c r="C270" t="n">
+        <v>256891.3776561468</v>
       </c>
     </row>
     <row r="271">
@@ -2598,7 +3410,10 @@
         <v>45196</v>
       </c>
       <c r="B271" t="n">
-        <v>212.2259443596908</v>
+        <v>257.3239575361251</v>
+      </c>
+      <c r="C271" t="n">
+        <v>257323.9575361251</v>
       </c>
     </row>
     <row r="272">
@@ -2606,7 +3421,10 @@
         <v>45197</v>
       </c>
       <c r="B272" t="n">
-        <v>212.5847713394922</v>
+        <v>257.7590352491343</v>
+      </c>
+      <c r="C272" t="n">
+        <v>257759.0352491343</v>
       </c>
     </row>
     <row r="273">
@@ -2614,7 +3432,10 @@
         <v>45198</v>
       </c>
       <c r="B273" t="n">
-        <v>212.9455520595944</v>
+        <v>258.1964818722583</v>
+      </c>
+      <c r="C273" t="n">
+        <v>258196.4818722583</v>
       </c>
     </row>
     <row r="274">
@@ -2622,7 +3443,10 @@
         <v>45199</v>
       </c>
       <c r="B274" t="n">
-        <v>213.3081796128838</v>
+        <v>258.6361677806216</v>
+      </c>
+      <c r="C274" t="n">
+        <v>258636.1677806216</v>
       </c>
     </row>
     <row r="275">
@@ -2630,7 +3454,10 @@
         <v>45200</v>
       </c>
       <c r="B275" t="n">
-        <v>213.6725465449902</v>
+        <v>259.0779626858007</v>
+      </c>
+      <c r="C275" t="n">
+        <v>259077.9626858007</v>
       </c>
     </row>
     <row r="276">
@@ -2638,7 +3465,10 @@
         <v>45201</v>
       </c>
       <c r="B276" t="n">
-        <v>214.038544886128</v>
+        <v>259.5217356744302</v>
+      </c>
+      <c r="C276" t="n">
+        <v>259521.7356744302</v>
       </c>
     </row>
     <row r="277">
@@ -2646,7 +3476,10 @@
         <v>45202</v>
       </c>
       <c r="B277" t="n">
-        <v>214.4060661830897</v>
+        <v>259.9673552469962</v>
+      </c>
+      <c r="C277" t="n">
+        <v>259967.3552469962</v>
       </c>
     </row>
     <row r="278">
@@ -2654,7 +3487,10 @@
         <v>45203</v>
       </c>
       <c r="B278" t="n">
-        <v>214.7750015313833</v>
+        <v>260.4146893568023</v>
+      </c>
+      <c r="C278" t="n">
+        <v>260414.6893568023</v>
       </c>
     </row>
     <row r="279">
@@ -2662,7 +3498,10 @@
         <v>45204</v>
       </c>
       <c r="B279" t="n">
-        <v>215.1452416075029</v>
+        <v>260.8636054490973</v>
+      </c>
+      <c r="C279" t="n">
+        <v>260863.6054490973</v>
       </c>
     </row>
     <row r="280">
@@ -2670,7 +3509,10 @@
         <v>45205</v>
       </c>
       <c r="B280" t="n">
-        <v>215.5166767013234</v>
+        <v>261.3139705003546</v>
+      </c>
+      <c r="C280" t="n">
+        <v>261313.9705003546</v>
       </c>
     </row>
     <row r="281">
@@ -2678,7 +3520,10 @@
         <v>45206</v>
       </c>
       <c r="B281" t="n">
-        <v>215.8891967486103</v>
+        <v>261.76565105769</v>
+      </c>
+      <c r="C281" t="n">
+        <v>261765.65105769</v>
       </c>
     </row>
     <row r="282">
@@ -2686,7 +3531,10 @@
         <v>45207</v>
       </c>
       <c r="B282" t="n">
-        <v>216.262691363634</v>
+        <v>262.2185132784063</v>
+      </c>
+      <c r="C282" t="n">
+        <v>262218.5132784063</v>
       </c>
     </row>
     <row r="283">
@@ -2694,7 +3542,10 @@
         <v>45208</v>
       </c>
       <c r="B283" t="n">
-        <v>216.6370498718794</v>
+        <v>262.6724229696538</v>
+      </c>
+      <c r="C283" t="n">
+        <v>262672.4229696539</v>
       </c>
     </row>
     <row r="284">
@@ -2702,7 +3553,10 @@
         <v>45209</v>
       </c>
       <c r="B284" t="n">
-        <v>217.0121613428412</v>
+        <v>263.1272456281949</v>
+      </c>
+      <c r="C284" t="n">
+        <v>263127.2456281949</v>
       </c>
     </row>
     <row r="285">
@@ -2710,7 +3564,10 @@
         <v>45210</v>
       </c>
       <c r="B285" t="n">
-        <v>217.3879146228948</v>
+        <v>263.58284648026</v>
+      </c>
+      <c r="C285" t="n">
+        <v>263582.84648026</v>
       </c>
     </row>
     <row r="286">
@@ -2718,7 +3575,10 @@
         <v>45211</v>
       </c>
       <c r="B286" t="n">
-        <v>217.7641983682342</v>
+        <v>264.0390905214839</v>
+      </c>
+      <c r="C286" t="n">
+        <v>264039.0905214839</v>
       </c>
     </row>
     <row r="287">
@@ -2726,7 +3586,10 @@
         <v>45212</v>
       </c>
       <c r="B287" t="n">
-        <v>218.1409010778645</v>
+        <v>264.4958425569107</v>
+      </c>
+      <c r="C287" t="n">
+        <v>264495.8425569107</v>
       </c>
     </row>
     <row r="288">
@@ -2734,7 +3597,10 @@
         <v>45213</v>
       </c>
       <c r="B288" t="n">
-        <v>218.5179111266431</v>
+        <v>264.9529672410548</v>
+      </c>
+      <c r="C288" t="n">
+        <v>264952.9672410548</v>
       </c>
     </row>
     <row r="289">
@@ -2742,7 +3608,10 @@
         <v>45214</v>
       </c>
       <c r="B289" t="n">
-        <v>218.895116798356</v>
+        <v>265.4103291180066</v>
+      </c>
+      <c r="C289" t="n">
+        <v>265410.3291180066</v>
       </c>
     </row>
     <row r="290">
@@ -2750,7 +3619,10 @@
         <v>45215</v>
       </c>
       <c r="B290" t="n">
-        <v>219.2724063188218</v>
+        <v>265.8677926615714</v>
+      </c>
+      <c r="C290" t="n">
+        <v>265867.7926615714</v>
       </c>
     </row>
     <row r="291">
@@ -2758,7 +3630,10 @@
         <v>45216</v>
       </c>
       <c r="B291" t="n">
-        <v>219.6496678890131</v>
+        <v>266.3252223154284</v>
+      </c>
+      <c r="C291" t="n">
+        <v>266325.2223154284</v>
       </c>
     </row>
     <row r="292">
@@ -2766,7 +3641,10 @@
         <v>45217</v>
       </c>
       <c r="B292" t="n">
-        <v>220.0267897181846</v>
+        <v>266.7824825332989</v>
+      </c>
+      <c r="C292" t="n">
+        <v>266782.4825332989</v>
       </c>
     </row>
     <row r="293">
@@ -2774,7 +3652,10 @@
         <v>45218</v>
       </c>
       <c r="B293" t="n">
-        <v>220.4036600569995</v>
+        <v>267.239437819112</v>
+      </c>
+      <c r="C293" t="n">
+        <v>267239.437819112</v>
       </c>
     </row>
     <row r="294">
@@ -2782,7 +3663,10 @@
         <v>45219</v>
       </c>
       <c r="B294" t="n">
-        <v>220.7801672306428</v>
+        <v>267.6959527671544</v>
+      </c>
+      <c r="C294" t="n">
+        <v>267695.9527671544</v>
       </c>
     </row>
     <row r="295">
@@ -2790,7 +3674,10 @@
         <v>45220</v>
       </c>
       <c r="B295" t="n">
-        <v>221.1561996719132</v>
+        <v>268.1518921021948</v>
+      </c>
+      <c r="C295" t="n">
+        <v>268151.8921021948</v>
       </c>
     </row>
     <row r="296">
@@ -2798,7 +3685,10 @@
         <v>45221</v>
       </c>
       <c r="B296" t="n">
-        <v>221.5316459542831</v>
+        <v>268.6071207195682</v>
+      </c>
+      <c r="C296" t="n">
+        <v>268607.1207195682</v>
       </c>
     </row>
     <row r="297">
@@ -2806,7 +3696,10 @@
         <v>45222</v>
       </c>
       <c r="B297" t="n">
-        <v>221.9063948249159</v>
+        <v>269.0615037252106</v>
+      </c>
+      <c r="C297" t="n">
+        <v>269061.5037252106</v>
       </c>
     </row>
     <row r="298">
@@ -2814,7 +3707,10 @@
         <v>45223</v>
       </c>
       <c r="B298" t="n">
-        <v>222.2803352376338</v>
+        <v>269.514906475631</v>
+      </c>
+      <c r="C298" t="n">
+        <v>269514.906475631</v>
       </c>
     </row>
     <row r="299">
@@ -2822,7 +3718,10 @@
         <v>45224</v>
       </c>
       <c r="B299" t="n">
-        <v>222.6533563858221</v>
+        <v>269.9671946178093</v>
+      </c>
+      <c r="C299" t="n">
+        <v>269967.1946178093</v>
       </c>
     </row>
     <row r="300">
@@ -2830,7 +3729,10 @@
         <v>45225</v>
       </c>
       <c r="B300" t="n">
-        <v>223.0253477352642</v>
+        <v>270.4182341290078</v>
+      </c>
+      <c r="C300" t="n">
+        <v>270418.2341290078</v>
       </c>
     </row>
     <row r="301">
@@ -2838,7 +3740,10 @@
         <v>45226</v>
       </c>
       <c r="B301" t="n">
-        <v>223.3961990568949</v>
+        <v>270.8678913564851</v>
+      </c>
+      <c r="C301" t="n">
+        <v>270867.8913564851</v>
       </c>
     </row>
     <row r="302">
@@ -2846,7 +3751,10 @@
         <v>45227</v>
       </c>
       <c r="B302" t="n">
-        <v>223.7658004594641</v>
+        <v>271.3160330571002</v>
+      </c>
+      <c r="C302" t="n">
+        <v>271316.0330571002</v>
       </c>
     </row>
     <row r="303">
@@ -2854,7 +3762,10 @@
         <v>45228</v>
       </c>
       <c r="B303" t="n">
-        <v>224.1340424220995</v>
+        <v>271.7625264367956</v>
+      </c>
+      <c r="C303" t="n">
+        <v>271762.5264367956</v>
       </c>
     </row>
     <row r="304">
@@ -2862,7 +3773,10 @@
         <v>45229</v>
       </c>
       <c r="B304" t="n">
-        <v>224.5008158267602</v>
+        <v>272.2072391899468</v>
+      </c>
+      <c r="C304" t="n">
+        <v>272207.2391899468</v>
       </c>
     </row>
     <row r="305">
@@ -2870,7 +3784,10 @@
         <v>45230</v>
       </c>
       <c r="B305" t="n">
-        <v>224.866011990571</v>
+        <v>272.6500395385673</v>
+      </c>
+      <c r="C305" t="n">
+        <v>272650.0395385673</v>
       </c>
     </row>
     <row r="306">
@@ -2878,7 +3795,10 @@
         <v>45231</v>
       </c>
       <c r="B306" t="n">
-        <v>225.2295226980267</v>
+        <v>273.0907962713574</v>
+      </c>
+      <c r="C306" t="n">
+        <v>273090.7962713573</v>
       </c>
     </row>
     <row r="307">
@@ -2886,7 +3806,10 @@
         <v>45232</v>
       </c>
       <c r="B307" t="n">
-        <v>225.5912402330597</v>
+        <v>273.5293787825849</v>
+      </c>
+      <c r="C307" t="n">
+        <v>273529.3787825849</v>
       </c>
     </row>
     <row r="308">
@@ -2894,7 +3817,10 @@
         <v>45233</v>
       </c>
       <c r="B308" t="n">
-        <v>225.9510574109577</v>
+        <v>273.9656571107863</v>
+      </c>
+      <c r="C308" t="n">
+        <v>273965.6571107862</v>
       </c>
     </row>
     <row r="309">
@@ -2902,7 +3828,10 @@
         <v>45234</v>
       </c>
       <c r="B309" t="n">
-        <v>226.3088676101256</v>
+        <v>274.3995019772773</v>
+      </c>
+      <c r="C309" t="n">
+        <v>274399.5019772773</v>
       </c>
     </row>
     <row r="310">
@@ -2910,7 +3839,10 @@
         <v>45235</v>
       </c>
       <c r="B310" t="n">
-        <v>226.664564803679</v>
+        <v>274.8307848244609</v>
+      </c>
+      <c r="C310" t="n">
+        <v>274830.7848244609</v>
       </c>
     </row>
     <row r="311">
@@ -2918,7 +3850,10 @@
         <v>45236</v>
       </c>
       <c r="B311" t="n">
-        <v>227.018043590863</v>
+        <v>275.2593778539214</v>
+      </c>
+      <c r="C311" t="n">
+        <v>275259.3778539214</v>
       </c>
     </row>
     <row r="312">
@@ -2926,7 +3861,10 @@
         <v>45237</v>
       </c>
       <c r="B312" t="n">
-        <v>227.3691992282843</v>
+        <v>275.6851540642947</v>
+      </c>
+      <c r="C312" t="n">
+        <v>275685.1540642947</v>
       </c>
     </row>
     <row r="313">
@@ -2934,7 +3872,10 @@
         <v>45238</v>
       </c>
       <c r="B313" t="n">
-        <v>227.7179276609487</v>
+        <v>276.1079872889003</v>
+      </c>
+      <c r="C313" t="n">
+        <v>276107.9872889004</v>
       </c>
     </row>
     <row r="314">
@@ -2942,7 +3883,10 @@
         <v>45239</v>
       </c>
       <c r="B314" t="n">
-        <v>228.0641255530958</v>
+        <v>276.5277522331288</v>
+      </c>
+      <c r="C314" t="n">
+        <v>276527.7522331288</v>
       </c>
     </row>
     <row r="315">
@@ -2950,7 +3894,10 @@
         <v>45240</v>
       </c>
       <c r="B315" t="n">
-        <v>228.4076903188184</v>
+        <v>276.9443245115673</v>
+      </c>
+      <c r="C315" t="n">
+        <v>276944.3245115674</v>
       </c>
     </row>
     <row r="316">
@@ -2958,7 +3905,10 @@
         <v>45241</v>
       </c>
       <c r="B316" t="n">
-        <v>228.7485201524617</v>
+        <v>277.3575806848598</v>
+      </c>
+      <c r="C316" t="n">
+        <v>277357.5806848598</v>
       </c>
     </row>
     <row r="317">
@@ -2966,7 +3916,10 @@
         <v>45242</v>
       </c>
       <c r="B317" t="n">
-        <v>229.0865140587902</v>
+        <v>277.7673982962831</v>
+      </c>
+      <c r="C317" t="n">
+        <v>277767.3982962832</v>
       </c>
     </row>
     <row r="318">
@@ -2974,7 +3927,10 @@
         <v>45243</v>
       </c>
       <c r="B318" t="n">
-        <v>229.4215718829151</v>
+        <v>278.1736559080346</v>
+      </c>
+      <c r="C318" t="n">
+        <v>278173.6559080345</v>
       </c>
     </row>
     <row r="319">
@@ -2982,7 +3938,10 @@
         <v>45244</v>
       </c>
       <c r="B319" t="n">
-        <v>229.7535943399719</v>
+        <v>278.5762331372159</v>
+      </c>
+      <c r="C319" t="n">
+        <v>278576.2331372159</v>
       </c>
     </row>
     <row r="320">
@@ -2990,7 +3949,10 @@
         <v>45245</v>
       </c>
       <c r="B320" t="n">
-        <v>230.0824830445409</v>
+        <v>278.9750106915059</v>
+      </c>
+      <c r="C320" t="n">
+        <v>278975.0106915059</v>
       </c>
     </row>
     <row r="321">
@@ -2998,7 +3960,10 @@
         <v>45246</v>
       </c>
       <c r="B321" t="n">
-        <v>230.4081405398011</v>
+        <v>279.3698704045088</v>
+      </c>
+      <c r="C321" t="n">
+        <v>279369.8704045088</v>
       </c>
     </row>
     <row r="322">
@@ -3006,7 +3971,10 @@
         <v>45247</v>
       </c>
       <c r="B322" t="n">
-        <v>230.7304703264082</v>
+        <v>279.7606952707699</v>
+      </c>
+      <c r="C322" t="n">
+        <v>279760.6952707699</v>
       </c>
     </row>
     <row r="323">
@@ -3014,7 +3982,10 @@
         <v>45248</v>
       </c>
       <c r="B323" t="n">
-        <v>231.04937689109</v>
+        <v>280.1473694804466</v>
+      </c>
+      <c r="C323" t="n">
+        <v>280147.3694804466</v>
       </c>
     </row>
     <row r="324">
@@ -3022,7 +3993,10 @@
         <v>45249</v>
       </c>
       <c r="B324" t="n">
-        <v>231.3647657349489</v>
+        <v>280.5297784536256</v>
+      </c>
+      <c r="C324" t="n">
+        <v>280529.7784536256</v>
       </c>
     </row>
     <row r="325">
@@ -3030,7 +4004,10 @@
         <v>45250</v>
       </c>
       <c r="B325" t="n">
-        <v>231.6765434014638</v>
+        <v>280.9078088742749</v>
+      </c>
+      <c r="C325" t="n">
+        <v>280907.8088742749</v>
       </c>
     </row>
     <row r="326">
@@ -3038,7 +4015,10 @@
         <v>45251</v>
       </c>
       <c r="B326" t="n">
-        <v>231.9846175041834</v>
+        <v>281.2813487238224</v>
+      </c>
+      <c r="C326" t="n">
+        <v>281281.3487238224</v>
       </c>
     </row>
     <row r="327">
@@ -3046,7 +4026,10 @@
         <v>45252</v>
       </c>
       <c r="B327" t="n">
-        <v>232.2888967541022</v>
+        <v>281.650287314349</v>
+      </c>
+      <c r="C327" t="n">
+        <v>281650.287314349</v>
       </c>
     </row>
     <row r="328">
@@ -3054,7 +4037,10 @@
         <v>45253</v>
       </c>
       <c r="B328" t="n">
-        <v>232.5892909867117</v>
+        <v>282.014515321388</v>
+      </c>
+      <c r="C328" t="n">
+        <v>282014.515321388</v>
       </c>
     </row>
     <row r="329">
@@ -3062,7 +4048,10 @@
         <v>45254</v>
       </c>
       <c r="B329" t="n">
-        <v>232.8857111887177</v>
+        <v>282.3739248163203</v>
+      </c>
+      <c r="C329" t="n">
+        <v>282373.9248163202</v>
       </c>
     </row>
     <row r="330">
@@ -3070,7 +4059,10 @@
         <v>45255</v>
       </c>
       <c r="B330" t="n">
-        <v>233.1780695244171</v>
+        <v>282.7284092983557</v>
+      </c>
+      <c r="C330" t="n">
+        <v>282728.4092983557</v>
       </c>
     </row>
     <row r="331">
@@ -3078,7 +4070,10 @@
         <v>45256</v>
       </c>
       <c r="B331" t="n">
-        <v>233.4662793617252</v>
+        <v>283.0778637260918</v>
+      </c>
+      <c r="C331" t="n">
+        <v>283077.8637260919</v>
       </c>
     </row>
     <row r="332">
@@ -3086,7 +4081,10 @@
         <v>45257</v>
       </c>
       <c r="B332" t="n">
-        <v>233.7502552978474</v>
+        <v>283.4221845486399</v>
+      </c>
+      <c r="C332" t="n">
+        <v>283422.1845486399</v>
       </c>
     </row>
     <row r="333">
@@ -3094,7 +4092,10 @@
         <v>45258</v>
       </c>
       <c r="B333" t="n">
-        <v>234.0299131845849</v>
+        <v>283.7612697363093</v>
+      </c>
+      <c r="C333" t="n">
+        <v>283761.2697363092</v>
       </c>
     </row>
     <row r="334">
@@ -3102,7 +4103,10 @@
         <v>45259</v>
       </c>
       <c r="B334" t="n">
-        <v>234.3051701532706</v>
+        <v>284.0950188108406</v>
+      </c>
+      <c r="C334" t="n">
+        <v>284095.0188108406</v>
       </c>
     </row>
     <row r="335">
@@ -3110,7 +4114,10 @@
         <v>45260</v>
       </c>
       <c r="B335" t="n">
-        <v>234.575944639324</v>
+        <v>284.4233328751803</v>
+      </c>
+      <c r="C335" t="n">
+        <v>284423.3328751803</v>
       </c>
     </row>
     <row r="336">
@@ -3118,7 +4125,10 @@
         <v>45261</v>
       </c>
       <c r="B336" t="n">
-        <v>234.8421564064211</v>
+        <v>284.7461146427855</v>
+      </c>
+      <c r="C336" t="n">
+        <v>284746.1146427855</v>
       </c>
     </row>
     <row r="337">
@@ -3126,7 +4136,10 @@
         <v>45262</v>
       </c>
       <c r="B337" t="n">
-        <v>235.1037265702699</v>
+        <v>285.0632684664523</v>
+      </c>
+      <c r="C337" t="n">
+        <v>285063.2684664523</v>
       </c>
     </row>
     <row r="338">
@@ -3134,7 +4147,10 @@
         <v>45263</v>
       </c>
       <c r="B338" t="n">
-        <v>235.3605776219859</v>
+        <v>285.3747003666579</v>
+      </c>
+      <c r="C338" t="n">
+        <v>285374.7003666579</v>
       </c>
     </row>
     <row r="339">
@@ -3142,7 +4158,10 @@
         <v>45264</v>
       </c>
       <c r="B339" t="n">
-        <v>235.612633451059</v>
+        <v>285.680318059409</v>
+      </c>
+      <c r="C339" t="n">
+        <v>285680.318059409</v>
       </c>
     </row>
     <row r="340">
@@ -3150,7 +4169,10 @@
         <v>45265</v>
       </c>
       <c r="B340" t="n">
-        <v>235.8598193679074</v>
+        <v>285.9800309835877</v>
+      </c>
+      <c r="C340" t="n">
+        <v>285980.0309835877</v>
       </c>
     </row>
     <row r="341">
@@ -3158,7 +4180,10 @@
         <v>45266</v>
       </c>
       <c r="B341" t="n">
-        <v>236.1020621260091</v>
+        <v>286.273750327786</v>
+      </c>
+      <c r="C341" t="n">
+        <v>286273.750327786</v>
       </c>
     </row>
     <row r="342">
@@ -3166,7 +4191,10 @@
         <v>45267</v>
       </c>
       <c r="B342" t="n">
-        <v>236.3392899436068</v>
+        <v>286.5613890566233</v>
+      </c>
+      <c r="C342" t="n">
+        <v>286561.3890566233</v>
       </c>
     </row>
     <row r="343">
@@ -3174,7 +4202,10 @@
         <v>45268</v>
       </c>
       <c r="B343" t="n">
-        <v>236.5714325249786</v>
+        <v>286.8428619365366</v>
+      </c>
+      <c r="C343" t="n">
+        <v>286842.8619365366</v>
       </c>
     </row>
     <row r="344">
@@ -3182,7 +4213,10 @@
         <v>45269</v>
       </c>
       <c r="B344" t="n">
-        <v>236.7984210812673</v>
+        <v>287.1180855610366</v>
+      </c>
+      <c r="C344" t="n">
+        <v>287118.0855610366</v>
       </c>
     </row>
     <row r="345">
@@ -3190,7 +4224,10 @@
         <v>45270</v>
       </c>
       <c r="B345" t="n">
-        <v>237.0201883508651</v>
+        <v>287.3869783754239</v>
+      </c>
+      <c r="C345" t="n">
+        <v>287386.9783754239</v>
       </c>
     </row>
     <row r="346">
@@ -3198,7 +4235,10 @@
         <v>45271</v>
       </c>
       <c r="B346" t="n">
-        <v>237.2366686193436</v>
+        <v>287.6494607009542</v>
+      </c>
+      <c r="C346" t="n">
+        <v>287649.4607009542</v>
       </c>
     </row>
     <row r="347">
@@ -3206,7 +4246,10 @@
         <v>45272</v>
       </c>
       <c r="B347" t="n">
-        <v>237.4477977389276</v>
+        <v>287.9054547584497</v>
+      </c>
+      <c r="C347" t="n">
+        <v>287905.4547584496</v>
       </c>
     </row>
     <row r="348">
@@ -3214,7 +4257,10 @@
         <v>45273</v>
       </c>
       <c r="B348" t="n">
-        <v>237.6535131475021</v>
+        <v>288.1548846913464</v>
+      </c>
+      <c r="C348" t="n">
+        <v>288154.8846913464</v>
       </c>
     </row>
     <row r="349">
@@ -3222,7 +4268,10 @@
         <v>45274</v>
       </c>
       <c r="B349" t="n">
-        <v>237.853753887152</v>
+        <v>288.3976765881717</v>
+      </c>
+      <c r="C349" t="n">
+        <v>288397.6765881717</v>
       </c>
     </row>
     <row r="350">
@@ -3230,7 +4279,10 @@
         <v>45275</v>
       </c>
       <c r="B350" t="n">
-        <v>238.0484606222245</v>
+        <v>288.6337585044473</v>
+      </c>
+      <c r="C350" t="n">
+        <v>288633.7585044472</v>
       </c>
     </row>
     <row r="351">
@@ -3238,7 +4290,10 @@
         <v>45276</v>
       </c>
       <c r="B351" t="n">
-        <v>238.237575656912</v>
+        <v>288.8630604840058</v>
+      </c>
+      <c r="C351" t="n">
+        <v>288863.0604840058</v>
       </c>
     </row>
     <row r="352">
@@ -3246,7 +4301,10 @@
         <v>45277</v>
       </c>
       <c r="B352" t="n">
-        <v>238.4210429523482</v>
+        <v>289.0855145797223</v>
+      </c>
+      <c r="C352" t="n">
+        <v>289085.5145797223</v>
       </c>
     </row>
     <row r="353">
@@ -3254,7 +4312,10 @@
         <v>45278</v>
       </c>
       <c r="B353" t="n">
-        <v>238.598808143214</v>
+        <v>289.301054873647</v>
+      </c>
+      <c r="C353" t="n">
+        <v>289301.054873647</v>
       </c>
     </row>
     <row r="354">
@@ -3262,7 +4323,10 @@
         <v>45279</v>
       </c>
       <c r="B354" t="n">
-        <v>238.7708185538467</v>
+        <v>289.5096174965391</v>
+      </c>
+      <c r="C354" t="n">
+        <v>289509.6174965391</v>
       </c>
     </row>
     <row r="355">
@@ -3270,7 +4334,10 @@
         <v>45280</v>
       </c>
       <c r="B355" t="n">
-        <v>238.9370232138495</v>
+        <v>289.7111406467926</v>
+      </c>
+      <c r="C355" t="n">
+        <v>289711.1406467925</v>
       </c>
     </row>
     <row r="356">
@@ -3278,7 +4345,10 @@
         <v>45281</v>
       </c>
       <c r="B356" t="n">
-        <v>239.0973728731946</v>
+        <v>289.9055646087484</v>
+      </c>
+      <c r="C356" t="n">
+        <v>289905.5646087484</v>
       </c>
     </row>
     <row r="357">
@@ -3286,7 +4356,10 @@
         <v>45282</v>
       </c>
       <c r="B357" t="n">
-        <v>239.2518200168172</v>
+        <v>290.0928317703909</v>
+      </c>
+      <c r="C357" t="n">
+        <v>290092.831770391</v>
       </c>
     </row>
     <row r="358">
@@ -3294,7 +4367,10 @@
         <v>45283</v>
       </c>
       <c r="B358" t="n">
-        <v>239.4003188786956</v>
+        <v>290.2728866404184</v>
+      </c>
+      <c r="C358" t="n">
+        <v>290272.8866404184</v>
       </c>
     </row>
     <row r="359">
@@ -3302,7 +4378,10 @@
         <v>45284</v>
       </c>
       <c r="B359" t="n">
-        <v>239.542825455412</v>
+        <v>290.4456758646871</v>
+      </c>
+      <c r="C359" t="n">
+        <v>290445.6758646871</v>
       </c>
     </row>
     <row r="360">
@@ -3310,7 +4389,10 @@
         <v>45285</v>
       </c>
       <c r="B360" t="n">
-        <v>239.6792975191923</v>
+        <v>290.6111482420206</v>
+      </c>
+      <c r="C360" t="n">
+        <v>290611.1482420206</v>
       </c>
     </row>
     <row r="361">
@@ -3318,7 +4400,10 @@
         <v>45286</v>
       </c>
       <c r="B361" t="n">
-        <v>239.8096946304185</v>
+        <v>290.7692547393825</v>
+      </c>
+      <c r="C361" t="n">
+        <v>290769.2547393825</v>
       </c>
     </row>
     <row r="362">
@@ -3326,7 +4411,10 @@
         <v>45287</v>
       </c>
       <c r="B362" t="n">
-        <v>239.9339781496126</v>
+        <v>290.9199485064053</v>
+      </c>
+      <c r="C362" t="n">
+        <v>290919.9485064053</v>
       </c>
     </row>
     <row r="363">
@@ -3334,7 +4422,10 @@
         <v>45288</v>
       </c>
       <c r="B363" t="n">
-        <v>240.0521112488854</v>
+        <v>291.0631848892735</v>
+      </c>
+      <c r="C363" t="n">
+        <v>291063.1848892735</v>
       </c>
     </row>
     <row r="364">
@@ -3342,7 +4433,10 @@
         <v>45289</v>
       </c>
       <c r="B364" t="n">
-        <v>240.1640589228502</v>
+        <v>291.1989214439558</v>
+      </c>
+      <c r="C364" t="n">
+        <v>291198.9214439559</v>
       </c>
     </row>
     <row r="365">
@@ -3350,7 +4444,10 @@
         <v>45290</v>
       </c>
       <c r="B365" t="n">
-        <v>240.269787998995</v>
+        <v>291.3271179487815</v>
+      </c>
+      <c r="C365" t="n">
+        <v>291327.1179487815</v>
       </c>
     </row>
     <row r="366">
@@ -3358,7 +4455,10 @@
         <v>45291</v>
       </c>
       <c r="B366" t="n">
-        <v>240.3692671475129</v>
+        <v>291.4477364163595</v>
+      </c>
+      <c r="C366" t="n">
+        <v>291447.7364163595</v>
       </c>
     </row>
   </sheetData>

--- a/data/a_Eingangsdaten/Wärme/Warmwasserbedarf_täglich_23.xlsx
+++ b/data/a_Eingangsdaten/Wärme/Warmwasserbedarf_täglich_23.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
         <v>44927</v>
       </c>
       <c r="B2" t="n">
-        <v>240.4624668905852</v>
+        <v>242.5665134758778</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +454,7 @@
         <v>44928</v>
       </c>
       <c r="B3" t="n">
-        <v>240.5493596111166</v>
+        <v>242.6541665077139</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         <v>44929</v>
       </c>
       <c r="B4" t="n">
-        <v>240.6299195609187</v>
+        <v>242.7354313570767</v>
       </c>
     </row>
     <row r="5">
@@ -470,7 +470,7 @@
         <v>44930</v>
       </c>
       <c r="B5" t="n">
-        <v>240.7041228683397</v>
+        <v>242.8102839434377</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +478,7 @@
         <v>44931</v>
       </c>
       <c r="B6" t="n">
-        <v>240.7719475453383</v>
+        <v>242.8787020863601</v>
       </c>
     </row>
     <row r="7">
@@ -486,7 +486,7 @@
         <v>44932</v>
       </c>
       <c r="B7" t="n">
-        <v>240.8333734939988</v>
+        <v>242.9406655120713</v>
       </c>
     </row>
     <row r="8">
@@ -494,7 +494,7 @@
         <v>44933</v>
       </c>
       <c r="B8" t="n">
-        <v>240.8883825124871</v>
+        <v>242.9961558594713</v>
       </c>
     </row>
     <row r="9">
@@ -502,7 +502,7 @@
         <v>44934</v>
       </c>
       <c r="B9" t="n">
-        <v>240.9369583004436</v>
+        <v>243.0451566855725</v>
       </c>
     </row>
     <row r="10">
@@ -510,7 +510,7 @@
         <v>44935</v>
       </c>
       <c r="B10" t="n">
-        <v>240.9790864638142</v>
+        <v>243.0876534703725</v>
       </c>
     </row>
     <row r="11">
@@ -518,7 +518,7 @@
         <v>44936</v>
       </c>
       <c r="B11" t="n">
-        <v>241.0147545191147</v>
+        <v>243.1236336211569</v>
       </c>
     </row>
     <row r="12">
@@ -526,7 +526,7 @@
         <v>44937</v>
       </c>
       <c r="B12" t="n">
-        <v>241.0439518971306</v>
+        <v>243.1530864762305</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>44938</v>
       </c>
       <c r="B13" t="n">
-        <v>241.0666699460488</v>
+        <v>243.1760033080767</v>
       </c>
     </row>
     <row r="14">
@@ -542,7 +542,7 @@
         <v>44939</v>
       </c>
       <c r="B14" t="n">
-        <v>241.0829019340209</v>
+        <v>243.1923773259436</v>
       </c>
     </row>
     <row r="15">
@@ -550,7 +550,7 @@
         <v>44940</v>
       </c>
       <c r="B15" t="n">
-        <v>241.0926430511587</v>
+        <v>243.2022036778563</v>
       </c>
     </row>
     <row r="16">
@@ -558,7 +558,7 @@
         <v>44941</v>
       </c>
       <c r="B16" t="n">
-        <v>241.0958904109589</v>
+        <v>243.2054794520548</v>
       </c>
     </row>
     <row r="17">
@@ -566,7 +566,7 @@
         <v>44942</v>
       </c>
       <c r="B17" t="n">
-        <v>241.0926430511587</v>
+        <v>243.2022036778563</v>
       </c>
     </row>
     <row r="18">
@@ -574,7 +574,7 @@
         <v>44943</v>
       </c>
       <c r="B18" t="n">
-        <v>241.0829019340209</v>
+        <v>243.1923773259436</v>
       </c>
     </row>
     <row r="19">
@@ -582,7 +582,7 @@
         <v>44944</v>
       </c>
       <c r="B19" t="n">
-        <v>241.0666699460488</v>
+        <v>243.1760033080767</v>
       </c>
     </row>
     <row r="20">
@@ -590,7 +590,7 @@
         <v>44945</v>
       </c>
       <c r="B20" t="n">
-        <v>241.0439518971306</v>
+        <v>243.1530864762305</v>
       </c>
     </row>
     <row r="21">
@@ -598,7 +598,7 @@
         <v>44946</v>
       </c>
       <c r="B21" t="n">
-        <v>241.0147545191147</v>
+        <v>243.1236336211569</v>
       </c>
     </row>
     <row r="22">
@@ -606,7 +606,7 @@
         <v>44947</v>
       </c>
       <c r="B22" t="n">
-        <v>240.9790864638142</v>
+        <v>243.0876534703725</v>
       </c>
     </row>
     <row r="23">
@@ -614,7 +614,7 @@
         <v>44948</v>
       </c>
       <c r="B23" t="n">
-        <v>240.9369583004436</v>
+        <v>243.0451566855725</v>
       </c>
     </row>
     <row r="24">
@@ -622,7 +622,7 @@
         <v>44949</v>
       </c>
       <c r="B24" t="n">
-        <v>240.8883825124871</v>
+        <v>242.9961558594713</v>
       </c>
     </row>
     <row r="25">
@@ -630,7 +630,7 @@
         <v>44950</v>
       </c>
       <c r="B25" t="n">
-        <v>240.8333734939988</v>
+        <v>242.9406655120713</v>
       </c>
     </row>
     <row r="26">
@@ -638,7 +638,7 @@
         <v>44951</v>
       </c>
       <c r="B26" t="n">
-        <v>240.7719475453383</v>
+        <v>242.8787020863601</v>
       </c>
     </row>
     <row r="27">
@@ -646,7 +646,7 @@
         <v>44952</v>
       </c>
       <c r="B27" t="n">
-        <v>240.7041228683397</v>
+        <v>242.8102839434377</v>
       </c>
     </row>
     <row r="28">
@@ -654,7 +654,7 @@
         <v>44953</v>
       </c>
       <c r="B28" t="n">
-        <v>240.6299195609187</v>
+        <v>242.7354313570767</v>
       </c>
     </row>
     <row r="29">
@@ -662,7 +662,7 @@
         <v>44954</v>
       </c>
       <c r="B29" t="n">
-        <v>240.5493596111166</v>
+        <v>242.6541665077139</v>
       </c>
     </row>
     <row r="30">
@@ -670,7 +670,7 @@
         <v>44955</v>
       </c>
       <c r="B30" t="n">
-        <v>240.4624668905852</v>
+        <v>242.5665134758778</v>
       </c>
     </row>
     <row r="31">
@@ -678,7 +678,7 @@
         <v>44956</v>
       </c>
       <c r="B31" t="n">
-        <v>240.3692671475129</v>
+        <v>242.4724982350537</v>
       </c>
     </row>
     <row r="32">
@@ -686,7 +686,7 @@
         <v>44957</v>
       </c>
       <c r="B32" t="n">
-        <v>240.269787998995</v>
+        <v>242.3721486439862</v>
       </c>
     </row>
     <row r="33">
@@ -694,7 +694,7 @@
         <v>44958</v>
       </c>
       <c r="B33" t="n">
-        <v>240.1640589228502</v>
+        <v>242.2654944384251</v>
       </c>
     </row>
     <row r="34">
@@ -702,7 +702,7 @@
         <v>44959</v>
       </c>
       <c r="B34" t="n">
-        <v>240.0521112488854</v>
+        <v>242.1525672223131</v>
       </c>
     </row>
     <row r="35">
@@ -710,7 +710,7 @@
         <v>44960</v>
       </c>
       <c r="B35" t="n">
-        <v>239.9339781496126</v>
+        <v>242.0334004584217</v>
       </c>
     </row>
     <row r="36">
@@ -718,7 +718,7 @@
         <v>44961</v>
       </c>
       <c r="B36" t="n">
-        <v>239.8096946304185</v>
+        <v>241.9080294584347</v>
       </c>
     </row>
     <row r="37">
@@ -726,7 +726,7 @@
         <v>44962</v>
       </c>
       <c r="B37" t="n">
-        <v>239.6792975191923</v>
+        <v>241.7764913724852</v>
       </c>
     </row>
     <row r="38">
@@ -734,7 +734,7 @@
         <v>44963</v>
       </c>
       <c r="B38" t="n">
-        <v>239.542825455412</v>
+        <v>241.6388251781469</v>
       </c>
     </row>
     <row r="39">
@@ -742,7 +742,7 @@
         <v>44964</v>
       </c>
       <c r="B39" t="n">
-        <v>239.4003188786956</v>
+        <v>241.4950716688842</v>
       </c>
     </row>
     <row r="40">
@@ -750,7 +750,7 @@
         <v>44965</v>
       </c>
       <c r="B40" t="n">
-        <v>239.2518200168172</v>
+        <v>241.3452734419644</v>
       </c>
     </row>
     <row r="41">
@@ -758,7 +758,7 @@
         <v>44966</v>
       </c>
       <c r="B41" t="n">
-        <v>239.0973728731946</v>
+        <v>241.189474885835</v>
       </c>
     </row>
     <row r="42">
@@ -766,7 +766,7 @@
         <v>44967</v>
       </c>
       <c r="B42" t="n">
-        <v>238.9370232138495</v>
+        <v>241.0277221669707</v>
       </c>
     </row>
     <row r="43">
@@ -774,7 +774,7 @@
         <v>44968</v>
       </c>
       <c r="B43" t="n">
-        <v>238.7708185538467</v>
+        <v>240.8600632161929</v>
       </c>
     </row>
     <row r="44">
@@ -782,7 +782,7 @@
         <v>44969</v>
       </c>
       <c r="B44" t="n">
-        <v>238.598808143214</v>
+        <v>240.6865477144671</v>
       </c>
     </row>
     <row r="45">
@@ -790,7 +790,7 @@
         <v>44970</v>
       </c>
       <c r="B45" t="n">
-        <v>238.4210429523482</v>
+        <v>240.5072270781813</v>
       </c>
     </row>
     <row r="46">
@@ -798,7 +798,7 @@
         <v>44971</v>
       </c>
       <c r="B46" t="n">
-        <v>238.237575656912</v>
+        <v>240.32215444391</v>
       </c>
     </row>
     <row r="47">
@@ -806,7 +806,7 @@
         <v>44972</v>
       </c>
       <c r="B47" t="n">
-        <v>238.0484606222245</v>
+        <v>240.131384652669</v>
       </c>
     </row>
     <row r="48">
@@ -814,7 +814,7 @@
         <v>44973</v>
       </c>
       <c r="B48" t="n">
-        <v>237.853753887152</v>
+        <v>239.9349742336645</v>
       </c>
     </row>
     <row r="49">
@@ -822,7 +822,7 @@
         <v>44974</v>
       </c>
       <c r="B49" t="n">
-        <v>237.6535131475021</v>
+        <v>239.7329813875427</v>
       </c>
     </row>
     <row r="50">
@@ -830,7 +830,7 @@
         <v>44975</v>
       </c>
       <c r="B50" t="n">
-        <v>237.4477977389276</v>
+        <v>239.5254659691432</v>
       </c>
     </row>
     <row r="51">
@@ -838,7 +838,7 @@
         <v>44976</v>
       </c>
       <c r="B51" t="n">
-        <v>237.2366686193436</v>
+        <v>239.3124894697629</v>
       </c>
     </row>
     <row r="52">
@@ -846,7 +846,7 @@
         <v>44977</v>
       </c>
       <c r="B52" t="n">
-        <v>237.0201883508651</v>
+        <v>239.0941149989351</v>
       </c>
     </row>
     <row r="53">
@@ -854,7 +854,7 @@
         <v>44978</v>
       </c>
       <c r="B53" t="n">
-        <v>236.7984210812673</v>
+        <v>238.8704072657284</v>
       </c>
     </row>
     <row r="54">
@@ -862,7 +862,7 @@
         <v>44979</v>
       </c>
       <c r="B54" t="n">
-        <v>236.5714325249786</v>
+        <v>238.6414325595722</v>
       </c>
     </row>
     <row r="55">
@@ -870,7 +870,7 @@
         <v>44980</v>
       </c>
       <c r="B55" t="n">
-        <v>236.3392899436068</v>
+        <v>238.4072587306134</v>
       </c>
     </row>
     <row r="56">
@@ -878,7 +878,7 @@
         <v>44981</v>
       </c>
       <c r="B56" t="n">
-        <v>236.1020621260091</v>
+        <v>238.1679551696116</v>
       </c>
     </row>
     <row r="57">
@@ -886,7 +886,7 @@
         <v>44982</v>
       </c>
       <c r="B57" t="n">
-        <v>235.8598193679074</v>
+        <v>237.9235927873766</v>
       </c>
     </row>
     <row r="58">
@@ -894,7 +894,7 @@
         <v>44983</v>
       </c>
       <c r="B58" t="n">
-        <v>235.6126334510591</v>
+        <v>237.6742439937558</v>
       </c>
     </row>
     <row r="59">
@@ -902,7 +902,7 @@
         <v>44984</v>
       </c>
       <c r="B59" t="n">
-        <v>235.3605776219859</v>
+        <v>237.4199826761783</v>
       </c>
     </row>
     <row r="60">
@@ -910,7 +910,7 @@
         <v>44985</v>
       </c>
       <c r="B60" t="n">
-        <v>235.1037265702699</v>
+        <v>237.1608841777598</v>
       </c>
     </row>
     <row r="61">
@@ -918,7 +918,7 @@
         <v>44986</v>
       </c>
       <c r="B61" t="n">
-        <v>234.8421564064211</v>
+        <v>236.8970252749772</v>
       </c>
     </row>
     <row r="62">
@@ -926,7 +926,7 @@
         <v>44987</v>
       </c>
       <c r="B62" t="n">
-        <v>234.575944639324</v>
+        <v>236.6284841549181</v>
       </c>
     </row>
     <row r="63">
@@ -934,7 +934,7 @@
         <v>44988</v>
       </c>
       <c r="B63" t="n">
-        <v>234.3051701532706</v>
+        <v>236.3553403921117</v>
       </c>
     </row>
     <row r="64">
@@ -942,7 +942,7 @@
         <v>44989</v>
       </c>
       <c r="B64" t="n">
-        <v>234.029913184585</v>
+        <v>236.0776749249501</v>
       </c>
     </row>
     <row r="65">
@@ -950,7 +950,7 @@
         <v>44990</v>
       </c>
       <c r="B65" t="n">
-        <v>233.7502552978474</v>
+        <v>235.7955700317035</v>
       </c>
     </row>
     <row r="66">
@@ -958,7 +958,7 @@
         <v>44991</v>
       </c>
       <c r="B66" t="n">
-        <v>233.4662793617252</v>
+        <v>235.5091093061403</v>
       </c>
     </row>
     <row r="67">
@@ -966,7 +966,7 @@
         <v>44992</v>
       </c>
       <c r="B67" t="n">
-        <v>233.1780695244171</v>
+        <v>235.2183776327557</v>
       </c>
     </row>
     <row r="68">
@@ -974,7 +974,7 @@
         <v>44993</v>
       </c>
       <c r="B68" t="n">
-        <v>232.8857111887177</v>
+        <v>234.923461161619</v>
       </c>
     </row>
     <row r="69">
@@ -982,7 +982,7 @@
         <v>44994</v>
       </c>
       <c r="B69" t="n">
-        <v>232.5892909867117</v>
+        <v>234.6244472828455</v>
       </c>
     </row>
     <row r="70">
@@ -990,7 +990,7 @@
         <v>44995</v>
       </c>
       <c r="B70" t="n">
-        <v>232.2888967541023</v>
+        <v>234.3214246007007</v>
       </c>
     </row>
     <row r="71">
@@ -998,7 +998,7 @@
         <v>44996</v>
       </c>
       <c r="B71" t="n">
-        <v>231.9846175041834</v>
+        <v>234.014482907345</v>
       </c>
     </row>
     <row r="72">
@@ -1006,7 +1006,7 @@
         <v>44997</v>
       </c>
       <c r="B72" t="n">
-        <v>231.6765434014638</v>
+        <v>233.7037131562266</v>
       </c>
     </row>
     <row r="73">
@@ -1014,7 +1014,7 @@
         <v>44998</v>
       </c>
       <c r="B73" t="n">
-        <v>231.3647657349489</v>
+        <v>233.3892074351297</v>
       </c>
     </row>
     <row r="74">
@@ -1022,7 +1022,7 @@
         <v>44999</v>
       </c>
       <c r="B74" t="n">
-        <v>231.04937689109</v>
+        <v>233.071058938887</v>
       </c>
     </row>
     <row r="75">
@@ -1030,7 +1030,7 @@
         <v>45000</v>
       </c>
       <c r="B75" t="n">
-        <v>230.7304703264082</v>
+        <v>232.7493619417642</v>
       </c>
     </row>
     <row r="76">
@@ -1038,7 +1038,7 @@
         <v>45001</v>
       </c>
       <c r="B76" t="n">
-        <v>230.4081405398011</v>
+        <v>232.4242117695243</v>
       </c>
     </row>
     <row r="77">
@@ -1046,7 +1046,7 @@
         <v>45002</v>
       </c>
       <c r="B77" t="n">
-        <v>230.0824830445409</v>
+        <v>232.0957047711807</v>
       </c>
     </row>
     <row r="78">
@@ -1054,7 +1054,7 @@
         <v>45003</v>
       </c>
       <c r="B78" t="n">
-        <v>229.7535943399719</v>
+        <v>231.7639382904466</v>
       </c>
     </row>
     <row r="79">
@@ -1062,7 +1062,7 @@
         <v>45004</v>
       </c>
       <c r="B79" t="n">
-        <v>229.4215718829151</v>
+        <v>231.4290106368906</v>
       </c>
     </row>
     <row r="80">
@@ -1070,7 +1070,7 @@
         <v>45005</v>
       </c>
       <c r="B80" t="n">
-        <v>229.0865140587902</v>
+        <v>231.0910210568046</v>
       </c>
     </row>
     <row r="81">
@@ -1078,7 +1078,7 @@
         <v>45006</v>
       </c>
       <c r="B81" t="n">
-        <v>228.7485201524617</v>
+        <v>230.7500697037957</v>
       </c>
     </row>
     <row r="82">
@@ -1086,7 +1086,7 @@
         <v>45007</v>
       </c>
       <c r="B82" t="n">
-        <v>228.4076903188184</v>
+        <v>230.4062576091081</v>
       </c>
     </row>
     <row r="83">
@@ -1094,7 +1094,7 @@
         <v>45008</v>
       </c>
       <c r="B83" t="n">
-        <v>228.0641255530958</v>
+        <v>230.0596866516854</v>
       </c>
     </row>
     <row r="84">
@@ -1102,7 +1102,7 @@
         <v>45009</v>
       </c>
       <c r="B84" t="n">
-        <v>227.7179276609488</v>
+        <v>229.7104595279821</v>
       </c>
     </row>
     <row r="85">
@@ -1110,7 +1110,7 @@
         <v>45010</v>
       </c>
       <c r="B85" t="n">
-        <v>227.3691992282842</v>
+        <v>229.3586797215317</v>
       </c>
     </row>
     <row r="86">
@@ -1118,7 +1118,7 @@
         <v>45011</v>
       </c>
       <c r="B86" t="n">
-        <v>227.018043590863</v>
+        <v>229.0044514722831</v>
       </c>
     </row>
     <row r="87">
@@ -1126,7 +1126,7 @@
         <v>45012</v>
       </c>
       <c r="B87" t="n">
-        <v>226.664564803679</v>
+        <v>228.6478797457112</v>
       </c>
     </row>
     <row r="88">
@@ -1134,7 +1134,7 @@
         <v>45013</v>
       </c>
       <c r="B88" t="n">
-        <v>226.3088676101256</v>
+        <v>228.2890702017142</v>
       </c>
     </row>
     <row r="89">
@@ -1142,7 +1142,7 @@
         <v>45014</v>
       </c>
       <c r="B89" t="n">
-        <v>225.9510574109577</v>
+        <v>227.9281291633036</v>
       </c>
     </row>
     <row r="90">
@@ -1150,7 +1150,7 @@
         <v>45015</v>
       </c>
       <c r="B90" t="n">
-        <v>225.5912402330597</v>
+        <v>227.565163585099</v>
       </c>
     </row>
     <row r="91">
@@ -1158,7 +1158,7 @@
         <v>45016</v>
       </c>
       <c r="B91" t="n">
-        <v>225.2295226980267</v>
+        <v>227.2002810216344</v>
       </c>
     </row>
     <row r="92">
@@ -1166,7 +1166,7 @@
         <v>45017</v>
       </c>
       <c r="B92" t="n">
-        <v>224.866011990571</v>
+        <v>226.8335895954885</v>
       </c>
     </row>
     <row r="93">
@@ -1174,7 +1174,7 @@
         <v>45018</v>
       </c>
       <c r="B93" t="n">
-        <v>224.5008158267602</v>
+        <v>226.4651979652444</v>
       </c>
     </row>
     <row r="94">
@@ -1182,7 +1182,7 @@
         <v>45019</v>
       </c>
       <c r="B94" t="n">
-        <v>224.1340424220995</v>
+        <v>226.0952152932928</v>
       </c>
     </row>
     <row r="95">
@@ -1190,7 +1190,7 @@
         <v>45020</v>
       </c>
       <c r="B95" t="n">
-        <v>223.7658004594641</v>
+        <v>225.7237512134844</v>
       </c>
     </row>
     <row r="96">
@@ -1198,7 +1198,7 @@
         <v>45021</v>
       </c>
       <c r="B96" t="n">
-        <v>223.3961990568949</v>
+        <v>225.3509157986427</v>
       </c>
     </row>
     <row r="97">
@@ -1206,7 +1206,7 @@
         <v>45022</v>
       </c>
       <c r="B97" t="n">
-        <v>223.0253477352642</v>
+        <v>224.9768195279477</v>
       </c>
     </row>
     <row r="98">
@@ -1214,7 +1214,7 @@
         <v>45023</v>
       </c>
       <c r="B98" t="n">
-        <v>222.6533563858221</v>
+        <v>224.6015732541981</v>
       </c>
     </row>
     <row r="99">
@@ -1222,7 +1222,7 @@
         <v>45024</v>
       </c>
       <c r="B99" t="n">
-        <v>222.2803352376338</v>
+        <v>224.2252881709631</v>
       </c>
     </row>
     <row r="100">
@@ -1230,7 +1230,7 @@
         <v>45025</v>
       </c>
       <c r="B100" t="n">
-        <v>221.9063948249159</v>
+        <v>223.8480757796339</v>
       </c>
     </row>
     <row r="101">
@@ -1238,7 +1238,7 @@
         <v>45026</v>
       </c>
       <c r="B101" t="n">
-        <v>221.5316459542831</v>
+        <v>223.470047856383</v>
       </c>
     </row>
     <row r="102">
@@ -1246,7 +1246,7 @@
         <v>45027</v>
       </c>
       <c r="B102" t="n">
-        <v>221.1561996719132</v>
+        <v>223.0913164190424</v>
       </c>
     </row>
     <row r="103">
@@ -1254,7 +1254,7 @@
         <v>45028</v>
       </c>
       <c r="B103" t="n">
-        <v>220.7801672306428</v>
+        <v>222.7119936939109</v>
       </c>
     </row>
     <row r="104">
@@ -1262,7 +1262,7 @@
         <v>45029</v>
       </c>
       <c r="B104" t="n">
-        <v>220.4036600569995</v>
+        <v>222.3321920824983</v>
       </c>
     </row>
     <row r="105">
@@ -1270,7 +1270,7 @@
         <v>45030</v>
       </c>
       <c r="B105" t="n">
-        <v>220.0267897181846</v>
+        <v>221.9520241282187</v>
       </c>
     </row>
     <row r="106">
@@ -1278,7 +1278,7 @@
         <v>45031</v>
       </c>
       <c r="B106" t="n">
-        <v>219.6496678890131</v>
+        <v>221.571602483042</v>
       </c>
     </row>
     <row r="107">
@@ -1286,7 +1286,7 @@
         <v>45032</v>
       </c>
       <c r="B107" t="n">
-        <v>219.2724063188218</v>
+        <v>221.1910398741115</v>
       </c>
     </row>
     <row r="108">
@@ -1294,7 +1294,7 @@
         <v>45033</v>
       </c>
       <c r="B108" t="n">
-        <v>218.895116798356</v>
+        <v>220.8104490703416</v>
       </c>
     </row>
     <row r="109">
@@ -1302,7 +1302,7 @@
         <v>45034</v>
       </c>
       <c r="B109" t="n">
-        <v>218.5179111266431</v>
+        <v>220.4299428490012</v>
       </c>
     </row>
     <row r="110">
@@ -1310,7 +1310,7 @@
         <v>45035</v>
       </c>
       <c r="B110" t="n">
-        <v>218.1409010778645</v>
+        <v>220.0496339622958</v>
       </c>
     </row>
     <row r="111">
@@ -1318,7 +1318,7 @@
         <v>45036</v>
       </c>
       <c r="B111" t="n">
-        <v>217.7641983682342</v>
+        <v>219.6696351039562</v>
       </c>
     </row>
     <row r="112">
@@ -1326,7 +1326,7 @@
         <v>45037</v>
       </c>
       <c r="B112" t="n">
-        <v>217.3879146228948</v>
+        <v>219.2900588758452</v>
       </c>
     </row>
     <row r="113">
@@ -1334,7 +1334,7 @@
         <v>45038</v>
       </c>
       <c r="B113" t="n">
-        <v>217.0121613428412</v>
+        <v>218.911017754591</v>
       </c>
     </row>
     <row r="114">
@@ -1342,7 +1342,7 @@
         <v>45039</v>
       </c>
       <c r="B114" t="n">
-        <v>216.6370498718794</v>
+        <v>218.5326240582584</v>
       </c>
     </row>
     <row r="115">
@@ -1350,7 +1350,7 @@
         <v>45040</v>
       </c>
       <c r="B115" t="n">
-        <v>216.262691363634</v>
+        <v>218.1549899130659</v>
       </c>
     </row>
     <row r="116">
@@ -1358,7 +1358,7 @@
         <v>45041</v>
       </c>
       <c r="B116" t="n">
-        <v>215.8891967486103</v>
+        <v>217.7782272201607</v>
       </c>
     </row>
     <row r="117">
@@ -1366,7 +1366,7 @@
         <v>45042</v>
       </c>
       <c r="B117" t="n">
-        <v>215.5166767013234</v>
+        <v>217.40244762246</v>
       </c>
     </row>
     <row r="118">
@@ -1374,7 +1374,7 @@
         <v>45043</v>
       </c>
       <c r="B118" t="n">
-        <v>215.1452416075029</v>
+        <v>217.0277624715685</v>
       </c>
     </row>
     <row r="119">
@@ -1382,7 +1382,7 @@
         <v>45044</v>
       </c>
       <c r="B119" t="n">
-        <v>214.7750015313833</v>
+        <v>216.6542827947829</v>
       </c>
     </row>
     <row r="120">
@@ -1390,7 +1390,7 @@
         <v>45045</v>
       </c>
       <c r="B120" t="n">
-        <v>214.4060661830897</v>
+        <v>216.2821192621917</v>
       </c>
     </row>
     <row r="121">
@@ -1398,7 +1398,7 @@
         <v>45046</v>
       </c>
       <c r="B121" t="n">
-        <v>214.038544886128</v>
+        <v>215.9113821538816</v>
       </c>
     </row>
     <row r="122">
@@ -1406,7 +1406,7 @@
         <v>45047</v>
       </c>
       <c r="B122" t="n">
-        <v>213.6725465449902</v>
+        <v>215.5421813272589</v>
       </c>
     </row>
     <row r="123">
@@ -1414,7 +1414,7 @@
         <v>45048</v>
       </c>
       <c r="B123" t="n">
-        <v>213.3081796128839</v>
+        <v>215.1746261844966</v>
       </c>
     </row>
     <row r="124">
@@ -1422,7 +1422,7 @@
         <v>45049</v>
       </c>
       <c r="B124" t="n">
-        <v>212.9455520595944</v>
+        <v>214.8088256401159</v>
       </c>
     </row>
     <row r="125">
@@ -1430,7 +1430,7 @@
         <v>45050</v>
       </c>
       <c r="B125" t="n">
-        <v>212.5847713394922</v>
+        <v>214.4448880887128</v>
       </c>
     </row>
     <row r="126">
@@ -1438,7 +1438,7 @@
         <v>45051</v>
       </c>
       <c r="B126" t="n">
-        <v>212.2259443596908</v>
+        <v>214.0829213728381</v>
       </c>
     </row>
     <row r="127">
@@ -1446,7 +1446,7 @@
         <v>45052</v>
       </c>
       <c r="B127" t="n">
-        <v>211.8691774483685</v>
+        <v>213.7230327510417</v>
       </c>
     </row>
     <row r="128">
@@ -1454,7 +1454,7 @@
         <v>45053</v>
       </c>
       <c r="B128" t="n">
-        <v>211.5145763232607</v>
+        <v>213.3653288660893</v>
       </c>
     </row>
     <row r="129">
@@ -1462,7 +1462,7 @@
         <v>45054</v>
       </c>
       <c r="B129" t="n">
-        <v>211.1622460603338</v>
+        <v>213.0099157133617</v>
       </c>
     </row>
     <row r="130">
@@ -1470,7 +1470,7 @@
         <v>45055</v>
       </c>
       <c r="B130" t="n">
-        <v>210.8122910626486</v>
+        <v>212.6568986094468</v>
       </c>
     </row>
     <row r="131">
@@ -1478,7 +1478,7 @@
         <v>45056</v>
       </c>
       <c r="B131" t="n">
-        <v>210.4648150294234</v>
+        <v>212.3063821609309</v>
       </c>
     </row>
     <row r="132">
@@ -1486,7 +1486,7 @@
         <v>45057</v>
       </c>
       <c r="B132" t="n">
-        <v>210.1199209253062</v>
+        <v>211.9584702334026</v>
       </c>
     </row>
     <row r="133">
@@ -1494,7 +1494,7 @@
         <v>45058</v>
       </c>
       <c r="B133" t="n">
-        <v>209.7777109498634</v>
+        <v>211.6132659206747</v>
       </c>
     </row>
     <row r="134">
@@ -1502,7 +1502,7 @@
         <v>45059</v>
       </c>
       <c r="B134" t="n">
-        <v>209.4382865072961</v>
+        <v>211.270871514235</v>
       </c>
     </row>
     <row r="135">
@@ -1510,7 +1510,7 @@
         <v>45060</v>
       </c>
       <c r="B135" t="n">
-        <v>209.1017481763922</v>
+        <v>210.9313884729357</v>
       </c>
     </row>
     <row r="136">
@@ -1518,7 +1518,7 @@
         <v>45061</v>
       </c>
       <c r="B136" t="n">
-        <v>208.7681956807222</v>
+        <v>210.5949173929285</v>
       </c>
     </row>
     <row r="137">
@@ -1526,7 +1526,7 @@
         <v>45062</v>
       </c>
       <c r="B137" t="n">
-        <v>208.4377278590891</v>
+        <v>210.2615579778561</v>
       </c>
     </row>
     <row r="138">
@@ -1534,7 +1534,7 @@
         <v>45063</v>
       </c>
       <c r="B138" t="n">
-        <v>208.1104426362407</v>
+        <v>209.9314090093078</v>
       </c>
     </row>
     <row r="139">
@@ -1542,7 +1542,7 @@
         <v>45064</v>
       </c>
       <c r="B139" t="n">
-        <v>207.7864369938517</v>
+        <v>209.6045683175479</v>
       </c>
     </row>
     <row r="140">
@@ -1550,7 +1550,7 @@
         <v>45065</v>
       </c>
       <c r="B140" t="n">
-        <v>207.4658069417868</v>
+        <v>209.2811327525274</v>
       </c>
     </row>
     <row r="141">
@@ -1558,7 +1558,7 @@
         <v>45066</v>
       </c>
       <c r="B141" t="n">
-        <v>207.14864748965</v>
+        <v>208.9611981551844</v>
       </c>
     </row>
     <row r="142">
@@ -1566,7 +1566,7 @@
         <v>45067</v>
       </c>
       <c r="B142" t="n">
-        <v>206.8350526186319</v>
+        <v>208.6448593290449</v>
       </c>
     </row>
     <row r="143">
@@ -1574,7 +1574,7 @@
         <v>45068</v>
       </c>
       <c r="B143" t="n">
-        <v>206.5251152536608</v>
+        <v>208.3322100121303</v>
       </c>
     </row>
     <row r="144">
@@ -1582,7 +1582,7 @@
         <v>45069</v>
       </c>
       <c r="B144" t="n">
-        <v>206.2189272358668</v>
+        <v>208.0233428491806</v>
       </c>
     </row>
     <row r="145">
@@ -1590,7 +1590,7 @@
         <v>45070</v>
       </c>
       <c r="B145" t="n">
-        <v>205.9165792953677</v>
+        <v>207.7183493642022</v>
       </c>
     </row>
     <row r="146">
@@ -1598,7 +1598,7 @@
         <v>45071</v>
       </c>
       <c r="B146" t="n">
-        <v>205.6181610243835</v>
+        <v>207.4173199333468</v>
       </c>
     </row>
     <row r="147">
@@ -1606,7 +1606,7 @@
         <v>45072</v>
       </c>
       <c r="B147" t="n">
-        <v>205.3237608506882</v>
+        <v>207.1203437581318</v>
       </c>
     </row>
     <row r="148">
@@ -1614,7 +1614,7 @@
         <v>45073</v>
       </c>
       <c r="B148" t="n">
-        <v>205.0334660114071</v>
+        <v>206.8275088390069</v>
       </c>
     </row>
     <row r="149">
@@ -1622,7 +1622,7 @@
         <v>45074</v>
       </c>
       <c r="B149" t="n">
-        <v>204.747362527166</v>
+        <v>206.5389019492788</v>
       </c>
     </row>
     <row r="150">
@@ -1630,7 +1630,7 @@
         <v>45075</v>
       </c>
       <c r="B150" t="n">
-        <v>204.465535176602</v>
+        <v>206.2546086093973</v>
       </c>
     </row>
     <row r="151">
@@ -1638,7 +1638,7 @@
         <v>45076</v>
       </c>
       <c r="B151" t="n">
-        <v>204.1880674712414</v>
+        <v>205.9747130616148</v>
       </c>
     </row>
     <row r="152">
@@ -1646,7 +1646,7 @@
         <v>45077</v>
       </c>
       <c r="B152" t="n">
-        <v>203.9150416307535</v>
+        <v>205.6992982450226</v>
       </c>
     </row>
     <row r="153">
@@ -1654,7 +1654,7 @@
         <v>45078</v>
       </c>
       <c r="B153" t="n">
-        <v>203.6465385585872</v>
+        <v>205.4284457709748</v>
       </c>
     </row>
     <row r="154">
@@ -1662,7 +1662,7 @@
         <v>45079</v>
       </c>
       <c r="B154" t="n">
-        <v>203.3826378179976</v>
+        <v>205.162235898905</v>
       </c>
     </row>
     <row r="155">
@@ -1670,7 +1670,7 @@
         <v>45080</v>
       </c>
       <c r="B155" t="n">
-        <v>203.1234176084695</v>
+        <v>204.9007475125436</v>
       </c>
     </row>
     <row r="156">
@@ -1678,7 +1678,7 @@
         <v>45081</v>
       </c>
       <c r="B156" t="n">
-        <v>202.8689547425455</v>
+        <v>204.6440580965428</v>
       </c>
     </row>
     <row r="157">
@@ -1686,7 +1686,7 @@
         <v>45082</v>
       </c>
       <c r="B157" t="n">
-        <v>202.6193246230645</v>
+        <v>204.3922437135163</v>
       </c>
     </row>
     <row r="158">
@@ -1694,7 +1694,7 @@
         <v>45083</v>
       </c>
       <c r="B158" t="n">
-        <v>202.3746012208184</v>
+        <v>204.1453789815006</v>
       </c>
     </row>
     <row r="159">
@@ -1702,7 +1702,7 @@
         <v>45084</v>
       </c>
       <c r="B159" t="n">
-        <v>202.1348570526328</v>
+        <v>203.9035370518434</v>
       </c>
     </row>
     <row r="160">
@@ -1710,7 +1710,7 @@
         <v>45085</v>
       </c>
       <c r="B160" t="n">
-        <v>201.9001631598789</v>
+        <v>203.6667895875278</v>
       </c>
     </row>
     <row r="161">
@@ -1718,7 +1718,7 @@
         <v>45086</v>
       </c>
       <c r="B161" t="n">
-        <v>201.6705890874221</v>
+        <v>203.4352067419371</v>
       </c>
     </row>
     <row r="162">
@@ -1726,7 +1726,7 @@
         <v>45087</v>
       </c>
       <c r="B162" t="n">
-        <v>201.4462028630149</v>
+        <v>203.2088571380662</v>
       </c>
     </row>
     <row r="163">
@@ -1734,7 +1734,7 @@
         <v>45088</v>
       </c>
       <c r="B163" t="n">
-        <v>201.227070977138</v>
+        <v>202.9878078481879</v>
       </c>
     </row>
     <row r="164">
@@ -1742,7 +1742,7 @@
         <v>45089</v>
       </c>
       <c r="B164" t="n">
-        <v>201.0132583632985</v>
+        <v>202.7721243739774</v>
       </c>
     </row>
     <row r="165">
@@ -1750,7 +1750,7 @@
         <v>45090</v>
       </c>
       <c r="B165" t="n">
-        <v>200.8048283787885</v>
+        <v>202.5618706271029</v>
       </c>
     </row>
     <row r="166">
@@ -1758,7 +1758,7 @@
         <v>45091</v>
       </c>
       <c r="B166" t="n">
-        <v>200.6018427859105</v>
+        <v>202.3571089102873</v>
       </c>
     </row>
     <row r="167">
@@ -1766,7 +1766,7 @@
         <v>45092</v>
       </c>
       <c r="B167" t="n">
-        <v>200.4043617336766</v>
+        <v>202.1578998988463</v>
       </c>
     </row>
     <row r="168">
@@ -1774,7 +1774,7 @@
         <v>45093</v>
       </c>
       <c r="B168" t="n">
-        <v>200.2124437399845</v>
+        <v>201.9643026227094</v>
       </c>
     </row>
     <row r="169">
@@ -1782,7 +1782,7 @@
         <v>45094</v>
       </c>
       <c r="B169" t="n">
-        <v>200.0261456742777</v>
+        <v>201.7763744489276</v>
       </c>
     </row>
     <row r="170">
@@ -1790,7 +1790,7 @@
         <v>45095</v>
       </c>
       <c r="B170" t="n">
-        <v>199.8455227406936</v>
+        <v>201.5941710646747</v>
       </c>
     </row>
     <row r="171">
@@ -1798,7 +1798,7 @@
         <v>45096</v>
       </c>
       <c r="B171" t="n">
-        <v>199.6706284617057</v>
+        <v>201.4177464607456</v>
       </c>
     </row>
     <row r="172">
@@ -1806,7 +1806,7 @@
         <v>45097</v>
       </c>
       <c r="B172" t="n">
-        <v>199.5015146622634</v>
+        <v>201.2471529155582</v>
       </c>
     </row>
     <row r="173">
@@ -1814,7 +1814,7 @@
         <v>45098</v>
       </c>
       <c r="B173" t="n">
-        <v>199.3382314544351</v>
+        <v>201.0824409796614</v>
       </c>
     </row>
     <row r="174">
@@ -1822,7 +1822,7 @@
         <v>45099</v>
       </c>
       <c r="B174" t="n">
-        <v>199.1808272225594</v>
+        <v>200.9236594607568</v>
       </c>
     </row>
     <row r="175">
@@ -1830,7 +1830,7 @@
         <v>45100</v>
       </c>
       <c r="B175" t="n">
-        <v>199.0293486089072</v>
+        <v>200.7708554092351</v>
       </c>
     </row>
     <row r="176">
@@ -1838,7 +1838,7 @@
         <v>45101</v>
       </c>
       <c r="B176" t="n">
-        <v>198.8838404998608</v>
+        <v>200.6240741042346</v>
       </c>
     </row>
     <row r="177">
@@ -1846,7 +1846,7 @@
         <v>45102</v>
       </c>
       <c r="B177" t="n">
-        <v>198.7443460126134</v>
+        <v>200.4833590402238</v>
       </c>
     </row>
     <row r="178">
@@ -1854,7 +1854,7 @@
         <v>45103</v>
       </c>
       <c r="B178" t="n">
-        <v>198.610906482392</v>
+        <v>200.3487519141129</v>
       </c>
     </row>
     <row r="179">
@@ -1862,7 +1862,7 @@
         <v>45104</v>
       </c>
       <c r="B179" t="n">
-        <v>198.4835614502093</v>
+        <v>200.2202926128986</v>
       </c>
     </row>
     <row r="180">
@@ -1870,7 +1870,7 @@
         <v>45105</v>
       </c>
       <c r="B180" t="n">
-        <v>198.3623486511467</v>
+        <v>200.0980192018442</v>
       </c>
     </row>
     <row r="181">
@@ -1878,7 +1878,7 @@
         <v>45106</v>
       </c>
       <c r="B181" t="n">
-        <v>198.2473040031725</v>
+        <v>199.9819679132002</v>
       </c>
     </row>
     <row r="182">
@@ -1886,7 +1886,7 @@
         <v>45107</v>
       </c>
       <c r="B182" t="n">
-        <v>198.1384615964987</v>
+        <v>199.8721731354681</v>
       </c>
     </row>
     <row r="183">
@@ -1894,7 +1894,7 @@
         <v>45108</v>
       </c>
       <c r="B183" t="n">
-        <v>198.0358536834796</v>
+        <v>199.7686674032101</v>
       </c>
     </row>
     <row r="184">
@@ -1902,7 +1902,7 @@
         <v>45109</v>
       </c>
       <c r="B184" t="n">
-        <v>197.9395106690541</v>
+        <v>199.6714813874083</v>
       </c>
     </row>
     <row r="185">
@@ -1910,7 +1910,7 @@
         <v>45110</v>
       </c>
       <c r="B185" t="n">
-        <v>197.8494611017367</v>
+        <v>199.5806438863769</v>
       </c>
     </row>
     <row r="186">
@@ -1918,7 +1918,7 @@
         <v>45111</v>
       </c>
       <c r="B186" t="n">
-        <v>197.7657316651577</v>
+        <v>199.4961818172278</v>
       </c>
     </row>
     <row r="187">
@@ -1926,7 +1926,7 @@
         <v>45112</v>
       </c>
       <c r="B187" t="n">
-        <v>197.688347170156</v>
+        <v>199.4181202078949</v>
       </c>
     </row>
     <row r="188">
@@ -1934,7 +1934,7 @@
         <v>45113</v>
       </c>
       <c r="B188" t="n">
-        <v>197.6173305474277</v>
+        <v>199.3464821897177</v>
       </c>
     </row>
     <row r="189">
@@ -1942,7 +1942,7 @@
         <v>45114</v>
       </c>
       <c r="B189" t="n">
-        <v>197.5527028407308</v>
+        <v>199.2812889905872</v>
       </c>
     </row>
     <row r="190">
@@ -1950,7 +1950,7 @@
         <v>45115</v>
       </c>
       <c r="B190" t="n">
-        <v>197.4944832006495</v>
+        <v>199.2225599286552</v>
       </c>
     </row>
     <row r="191">
@@ -1958,7 +1958,7 @@
         <v>45116</v>
       </c>
       <c r="B191" t="n">
-        <v>197.4426888789197</v>
+        <v>199.1703124066102</v>
       </c>
     </row>
     <row r="192">
@@ -1966,7 +1966,7 @@
         <v>45117</v>
       </c>
       <c r="B192" t="n">
-        <v>197.3973352233166</v>
+        <v>199.1245619065207</v>
       </c>
     </row>
     <row r="193">
@@ -1974,7 +1974,7 @@
         <v>45118</v>
       </c>
       <c r="B193" t="n">
-        <v>197.3584356731074</v>
+        <v>199.0853219852471</v>
       </c>
     </row>
     <row r="194">
@@ -1982,7 +1982,7 @@
         <v>45119</v>
       </c>
       <c r="B194" t="n">
-        <v>197.3260017550682</v>
+        <v>199.052604270425</v>
       </c>
     </row>
     <row r="195">
@@ -1990,7 +1990,7 @@
         <v>45120</v>
       </c>
       <c r="B195" t="n">
-        <v>197.3000430800689</v>
+        <v>199.0264184570195</v>
       </c>
     </row>
     <row r="196">
@@ -1998,7 +1998,7 @@
         <v>45121</v>
       </c>
       <c r="B196" t="n">
-        <v>197.2805673402251</v>
+        <v>199.0067723044521</v>
       </c>
     </row>
     <row r="197">
@@ -2006,7 +2006,7 @@
         <v>45122</v>
       </c>
       <c r="B197" t="n">
-        <v>197.2675803066189</v>
+        <v>198.9936716343018</v>
       </c>
     </row>
     <row r="198">
@@ -2014,7 +2014,7 @@
         <v>45123</v>
       </c>
       <c r="B198" t="n">
-        <v>197.2610858275887</v>
+        <v>198.9871203285801</v>
       </c>
     </row>
     <row r="199">
@@ -2022,7 +2022,7 @@
         <v>45124</v>
       </c>
       <c r="B199" t="n">
-        <v>197.2610858275887</v>
+        <v>198.9871203285801</v>
       </c>
     </row>
     <row r="200">
@@ -2030,7 +2030,7 @@
         <v>45125</v>
       </c>
       <c r="B200" t="n">
-        <v>197.2675803066189</v>
+        <v>198.9936716343018</v>
       </c>
     </row>
     <row r="201">
@@ -2038,7 +2038,7 @@
         <v>45126</v>
       </c>
       <c r="B201" t="n">
-        <v>197.2805673402251</v>
+        <v>199.0067723044521</v>
       </c>
     </row>
     <row r="202">
@@ -2046,7 +2046,7 @@
         <v>45127</v>
       </c>
       <c r="B202" t="n">
-        <v>197.3000430800689</v>
+        <v>199.0264184570195</v>
       </c>
     </row>
     <row r="203">
@@ -2054,7 +2054,7 @@
         <v>45128</v>
       </c>
       <c r="B203" t="n">
-        <v>197.3260017550682</v>
+        <v>199.052604270425</v>
       </c>
     </row>
     <row r="204">
@@ -2062,7 +2062,7 @@
         <v>45129</v>
       </c>
       <c r="B204" t="n">
-        <v>197.3584356731074</v>
+        <v>199.0853219852471</v>
       </c>
     </row>
     <row r="205">
@@ -2070,7 +2070,7 @@
         <v>45130</v>
       </c>
       <c r="B205" t="n">
-        <v>197.3973352233166</v>
+        <v>199.1245619065207</v>
       </c>
     </row>
     <row r="206">
@@ -2078,7 +2078,7 @@
         <v>45131</v>
       </c>
       <c r="B206" t="n">
-        <v>197.4426888789197</v>
+        <v>199.1703124066102</v>
       </c>
     </row>
     <row r="207">
@@ -2086,7 +2086,7 @@
         <v>45132</v>
       </c>
       <c r="B207" t="n">
-        <v>197.4944832006495</v>
+        <v>199.2225599286552</v>
       </c>
     </row>
     <row r="208">
@@ -2094,7 +2094,7 @@
         <v>45133</v>
       </c>
       <c r="B208" t="n">
-        <v>197.5527028407308</v>
+        <v>199.2812889905872</v>
       </c>
     </row>
     <row r="209">
@@ -2102,7 +2102,7 @@
         <v>45134</v>
       </c>
       <c r="B209" t="n">
-        <v>197.6173305474277</v>
+        <v>199.3464821897177</v>
       </c>
     </row>
     <row r="210">
@@ -2110,7 +2110,7 @@
         <v>45135</v>
       </c>
       <c r="B210" t="n">
-        <v>197.688347170156</v>
+        <v>199.4181202078949</v>
       </c>
     </row>
     <row r="211">
@@ -2118,7 +2118,7 @@
         <v>45136</v>
       </c>
       <c r="B211" t="n">
-        <v>197.7657316651577</v>
+        <v>199.4961818172278</v>
       </c>
     </row>
     <row r="212">
@@ -2126,7 +2126,7 @@
         <v>45137</v>
       </c>
       <c r="B212" t="n">
-        <v>197.8494611017367</v>
+        <v>199.5806438863769</v>
       </c>
     </row>
     <row r="213">
@@ -2134,7 +2134,7 @@
         <v>45138</v>
       </c>
       <c r="B213" t="n">
-        <v>197.9395106690541</v>
+        <v>199.6714813874083</v>
       </c>
     </row>
     <row r="214">
@@ -2142,7 +2142,7 @@
         <v>45139</v>
       </c>
       <c r="B214" t="n">
-        <v>198.0358536834796</v>
+        <v>199.7686674032101</v>
       </c>
     </row>
     <row r="215">
@@ -2150,7 +2150,7 @@
         <v>45140</v>
       </c>
       <c r="B215" t="n">
-        <v>198.1384615964987</v>
+        <v>199.8721731354681</v>
       </c>
     </row>
     <row r="216">
@@ -2158,7 +2158,7 @@
         <v>45141</v>
       </c>
       <c r="B216" t="n">
-        <v>198.2473040031725</v>
+        <v>199.9819679132002</v>
       </c>
     </row>
     <row r="217">
@@ -2166,7 +2166,7 @@
         <v>45142</v>
       </c>
       <c r="B217" t="n">
-        <v>198.3623486511467</v>
+        <v>200.0980192018442</v>
       </c>
     </row>
     <row r="218">
@@ -2174,7 +2174,7 @@
         <v>45143</v>
       </c>
       <c r="B218" t="n">
-        <v>198.4835614502093</v>
+        <v>200.2202926128986</v>
       </c>
     </row>
     <row r="219">
@@ -2182,7 +2182,7 @@
         <v>45144</v>
       </c>
       <c r="B219" t="n">
-        <v>198.610906482392</v>
+        <v>200.3487519141129</v>
       </c>
     </row>
     <row r="220">
@@ -2190,7 +2190,7 @@
         <v>45145</v>
       </c>
       <c r="B220" t="n">
-        <v>198.7443460126134</v>
+        <v>200.4833590402238</v>
       </c>
     </row>
     <row r="221">
@@ -2198,7 +2198,7 @@
         <v>45146</v>
       </c>
       <c r="B221" t="n">
-        <v>198.8838404998608</v>
+        <v>200.6240741042346</v>
       </c>
     </row>
     <row r="222">
@@ -2206,7 +2206,7 @@
         <v>45147</v>
       </c>
       <c r="B222" t="n">
-        <v>199.0293486089072</v>
+        <v>200.7708554092351</v>
       </c>
     </row>
     <row r="223">
@@ -2214,7 +2214,7 @@
         <v>45148</v>
       </c>
       <c r="B223" t="n">
-        <v>199.1808272225594</v>
+        <v>200.9236594607568</v>
       </c>
     </row>
     <row r="224">
@@ -2222,7 +2222,7 @@
         <v>45149</v>
       </c>
       <c r="B224" t="n">
-        <v>199.3382314544351</v>
+        <v>201.0824409796614</v>
       </c>
     </row>
     <row r="225">
@@ -2230,7 +2230,7 @@
         <v>45150</v>
       </c>
       <c r="B225" t="n">
-        <v>199.5015146622634</v>
+        <v>201.2471529155582</v>
       </c>
     </row>
     <row r="226">
@@ -2238,7 +2238,7 @@
         <v>45151</v>
       </c>
       <c r="B226" t="n">
-        <v>199.6706284617057</v>
+        <v>201.4177464607456</v>
       </c>
     </row>
     <row r="227">
@@ -2246,7 +2246,7 @@
         <v>45152</v>
       </c>
       <c r="B227" t="n">
-        <v>199.8455227406936</v>
+        <v>201.5941710646747</v>
       </c>
     </row>
     <row r="228">
@@ -2254,7 +2254,7 @@
         <v>45153</v>
       </c>
       <c r="B228" t="n">
-        <v>200.0261456742777</v>
+        <v>201.7763744489276</v>
       </c>
     </row>
     <row r="229">
@@ -2262,7 +2262,7 @@
         <v>45154</v>
       </c>
       <c r="B229" t="n">
-        <v>200.2124437399845</v>
+        <v>201.9643026227094</v>
       </c>
     </row>
     <row r="230">
@@ -2270,7 +2270,7 @@
         <v>45155</v>
       </c>
       <c r="B230" t="n">
-        <v>200.4043617336766</v>
+        <v>202.1578998988463</v>
       </c>
     </row>
     <row r="231">
@@ -2278,7 +2278,7 @@
         <v>45156</v>
       </c>
       <c r="B231" t="n">
-        <v>200.6018427859105</v>
+        <v>202.3571089102873</v>
       </c>
     </row>
     <row r="232">
@@ -2286,7 +2286,7 @@
         <v>45157</v>
       </c>
       <c r="B232" t="n">
-        <v>200.8048283787885</v>
+        <v>202.5618706271029</v>
       </c>
     </row>
     <row r="233">
@@ -2294,7 +2294,7 @@
         <v>45158</v>
       </c>
       <c r="B233" t="n">
-        <v>201.0132583632985</v>
+        <v>202.7721243739774</v>
       </c>
     </row>
     <row r="234">
@@ -2302,7 +2302,7 @@
         <v>45159</v>
       </c>
       <c r="B234" t="n">
-        <v>201.227070977138</v>
+        <v>202.9878078481879</v>
       </c>
     </row>
     <row r="235">
@@ -2310,7 +2310,7 @@
         <v>45160</v>
       </c>
       <c r="B235" t="n">
-        <v>201.4462028630149</v>
+        <v>203.2088571380662</v>
       </c>
     </row>
     <row r="236">
@@ -2318,7 +2318,7 @@
         <v>45161</v>
       </c>
       <c r="B236" t="n">
-        <v>201.6705890874221</v>
+        <v>203.4352067419371</v>
       </c>
     </row>
     <row r="237">
@@ -2326,7 +2326,7 @@
         <v>45162</v>
       </c>
       <c r="B237" t="n">
-        <v>201.9001631598789</v>
+        <v>203.6667895875278</v>
       </c>
     </row>
     <row r="238">
@@ -2334,7 +2334,7 @@
         <v>45163</v>
       </c>
       <c r="B238" t="n">
-        <v>202.1348570526328</v>
+        <v>203.9035370518434</v>
       </c>
     </row>
     <row r="239">
@@ -2342,7 +2342,7 @@
         <v>45164</v>
       </c>
       <c r="B239" t="n">
-        <v>202.3746012208184</v>
+        <v>204.1453789815006</v>
       </c>
     </row>
     <row r="240">
@@ -2350,7 +2350,7 @@
         <v>45165</v>
       </c>
       <c r="B240" t="n">
-        <v>202.6193246230645</v>
+        <v>204.3922437135163</v>
       </c>
     </row>
     <row r="241">
@@ -2358,7 +2358,7 @@
         <v>45166</v>
       </c>
       <c r="B241" t="n">
-        <v>202.8689547425455</v>
+        <v>204.6440580965428</v>
       </c>
     </row>
     <row r="242">
@@ -2366,7 +2366,7 @@
         <v>45167</v>
       </c>
       <c r="B242" t="n">
-        <v>203.1234176084695</v>
+        <v>204.9007475125436</v>
       </c>
     </row>
     <row r="243">
@@ -2374,7 +2374,7 @@
         <v>45168</v>
       </c>
       <c r="B243" t="n">
-        <v>203.3826378179975</v>
+        <v>205.162235898905</v>
       </c>
     </row>
     <row r="244">
@@ -2382,7 +2382,7 @@
         <v>45169</v>
       </c>
       <c r="B244" t="n">
-        <v>203.6465385585872</v>
+        <v>205.4284457709748</v>
       </c>
     </row>
     <row r="245">
@@ -2390,7 +2390,7 @@
         <v>45170</v>
       </c>
       <c r="B245" t="n">
-        <v>203.9150416307534</v>
+        <v>205.6992982450226</v>
       </c>
     </row>
     <row r="246">
@@ -2398,7 +2398,7 @@
         <v>45171</v>
       </c>
       <c r="B246" t="n">
-        <v>204.1880674712414</v>
+        <v>205.9747130616148</v>
       </c>
     </row>
     <row r="247">
@@ -2406,7 +2406,7 @@
         <v>45172</v>
       </c>
       <c r="B247" t="n">
-        <v>204.465535176602</v>
+        <v>206.2546086093973</v>
       </c>
     </row>
     <row r="248">
@@ -2414,7 +2414,7 @@
         <v>45173</v>
       </c>
       <c r="B248" t="n">
-        <v>204.747362527166</v>
+        <v>206.5389019492788</v>
       </c>
     </row>
     <row r="249">
@@ -2422,7 +2422,7 @@
         <v>45174</v>
       </c>
       <c r="B249" t="n">
-        <v>205.0334660114071</v>
+        <v>206.8275088390069</v>
       </c>
     </row>
     <row r="250">
@@ -2430,7 +2430,7 @@
         <v>45175</v>
       </c>
       <c r="B250" t="n">
-        <v>205.3237608506882</v>
+        <v>207.1203437581318</v>
       </c>
     </row>
     <row r="251">
@@ -2438,7 +2438,7 @@
         <v>45176</v>
       </c>
       <c r="B251" t="n">
-        <v>205.6181610243835</v>
+        <v>207.4173199333468</v>
       </c>
     </row>
     <row r="252">
@@ -2446,7 +2446,7 @@
         <v>45177</v>
       </c>
       <c r="B252" t="n">
-        <v>205.9165792953677</v>
+        <v>207.7183493642021</v>
       </c>
     </row>
     <row r="253">
@@ -2454,7 +2454,7 @@
         <v>45178</v>
       </c>
       <c r="B253" t="n">
-        <v>206.2189272358668</v>
+        <v>208.0233428491806</v>
       </c>
     </row>
     <row r="254">
@@ -2462,7 +2462,7 @@
         <v>45179</v>
       </c>
       <c r="B254" t="n">
-        <v>206.5251152536608</v>
+        <v>208.3322100121303</v>
       </c>
     </row>
     <row r="255">
@@ -2470,7 +2470,7 @@
         <v>45180</v>
       </c>
       <c r="B255" t="n">
-        <v>206.8350526186319</v>
+        <v>208.6448593290449</v>
       </c>
     </row>
     <row r="256">
@@ -2478,7 +2478,7 @@
         <v>45181</v>
       </c>
       <c r="B256" t="n">
-        <v>207.14864748965</v>
+        <v>208.9611981551844</v>
       </c>
     </row>
     <row r="257">
@@ -2486,7 +2486,7 @@
         <v>45182</v>
       </c>
       <c r="B257" t="n">
-        <v>207.4658069417868</v>
+        <v>209.2811327525274</v>
       </c>
     </row>
     <row r="258">
@@ -2494,7 +2494,7 @@
         <v>45183</v>
       </c>
       <c r="B258" t="n">
-        <v>207.7864369938517</v>
+        <v>209.6045683175479</v>
       </c>
     </row>
     <row r="259">
@@ -2502,7 +2502,7 @@
         <v>45184</v>
       </c>
       <c r="B259" t="n">
-        <v>208.1104426362407</v>
+        <v>209.9314090093078</v>
       </c>
     </row>
     <row r="260">
@@ -2510,7 +2510,7 @@
         <v>45185</v>
       </c>
       <c r="B260" t="n">
-        <v>208.4377278590891</v>
+        <v>210.2615579778561</v>
       </c>
     </row>
     <row r="261">
@@ -2518,7 +2518,7 @@
         <v>45186</v>
       </c>
       <c r="B261" t="n">
-        <v>208.7681956807222</v>
+        <v>210.5949173929285</v>
       </c>
     </row>
     <row r="262">
@@ -2526,7 +2526,7 @@
         <v>45187</v>
       </c>
       <c r="B262" t="n">
-        <v>209.1017481763922</v>
+        <v>210.9313884729357</v>
       </c>
     </row>
     <row r="263">
@@ -2534,7 +2534,7 @@
         <v>45188</v>
       </c>
       <c r="B263" t="n">
-        <v>209.4382865072961</v>
+        <v>211.270871514235</v>
       </c>
     </row>
     <row r="264">
@@ -2542,7 +2542,7 @@
         <v>45189</v>
       </c>
       <c r="B264" t="n">
-        <v>209.7777109498633</v>
+        <v>211.6132659206746</v>
       </c>
     </row>
     <row r="265">
@@ -2550,7 +2550,7 @@
         <v>45190</v>
       </c>
       <c r="B265" t="n">
-        <v>210.1199209253062</v>
+        <v>211.9584702334026</v>
       </c>
     </row>
     <row r="266">
@@ -2558,7 +2558,7 @@
         <v>45191</v>
       </c>
       <c r="B266" t="n">
-        <v>210.4648150294234</v>
+        <v>212.3063821609309</v>
       </c>
     </row>
     <row r="267">
@@ -2566,7 +2566,7 @@
         <v>45192</v>
       </c>
       <c r="B267" t="n">
-        <v>210.8122910626486</v>
+        <v>212.6568986094468</v>
       </c>
     </row>
     <row r="268">
@@ -2574,7 +2574,7 @@
         <v>45193</v>
       </c>
       <c r="B268" t="n">
-        <v>211.1622460603338</v>
+        <v>213.0099157133617</v>
       </c>
     </row>
     <row r="269">
@@ -2582,7 +2582,7 @@
         <v>45194</v>
       </c>
       <c r="B269" t="n">
-        <v>211.5145763232607</v>
+        <v>213.3653288660893</v>
       </c>
     </row>
     <row r="270">
@@ -2590,7 +2590,7 @@
         <v>45195</v>
       </c>
       <c r="B270" t="n">
-        <v>211.8691774483685</v>
+        <v>213.7230327510417</v>
       </c>
     </row>
     <row r="271">
@@ -2598,7 +2598,7 @@
         <v>45196</v>
       </c>
       <c r="B271" t="n">
-        <v>212.2259443596908</v>
+        <v>214.0829213728381</v>
       </c>
     </row>
     <row r="272">
@@ -2606,7 +2606,7 @@
         <v>45197</v>
       </c>
       <c r="B272" t="n">
-        <v>212.5847713394922</v>
+        <v>214.4448880887128</v>
       </c>
     </row>
     <row r="273">
@@ -2614,7 +2614,7 @@
         <v>45198</v>
       </c>
       <c r="B273" t="n">
-        <v>212.9455520595944</v>
+        <v>214.8088256401159</v>
       </c>
     </row>
     <row r="274">
@@ -2622,7 +2622,7 @@
         <v>45199</v>
       </c>
       <c r="B274" t="n">
-        <v>213.3081796128838</v>
+        <v>215.1746261844966</v>
       </c>
     </row>
     <row r="275">
@@ -2630,7 +2630,7 @@
         <v>45200</v>
       </c>
       <c r="B275" t="n">
-        <v>213.6725465449902</v>
+        <v>215.5421813272589</v>
       </c>
     </row>
     <row r="276">
@@ -2638,7 +2638,7 @@
         <v>45201</v>
       </c>
       <c r="B276" t="n">
-        <v>214.038544886128</v>
+        <v>215.9113821538816</v>
       </c>
     </row>
     <row r="277">
@@ -2646,7 +2646,7 @@
         <v>45202</v>
       </c>
       <c r="B277" t="n">
-        <v>214.4060661830897</v>
+        <v>216.2821192621917</v>
       </c>
     </row>
     <row r="278">
@@ -2654,7 +2654,7 @@
         <v>45203</v>
       </c>
       <c r="B278" t="n">
-        <v>214.7750015313833</v>
+        <v>216.6542827947829</v>
       </c>
     </row>
     <row r="279">
@@ -2662,7 +2662,7 @@
         <v>45204</v>
       </c>
       <c r="B279" t="n">
-        <v>215.1452416075029</v>
+        <v>217.0277624715686</v>
       </c>
     </row>
     <row r="280">
@@ -2670,7 +2670,7 @@
         <v>45205</v>
       </c>
       <c r="B280" t="n">
-        <v>215.5166767013234</v>
+        <v>217.40244762246</v>
       </c>
     </row>
     <row r="281">
@@ -2678,7 +2678,7 @@
         <v>45206</v>
       </c>
       <c r="B281" t="n">
-        <v>215.8891967486103</v>
+        <v>217.7782272201607</v>
       </c>
     </row>
     <row r="282">
@@ -2686,7 +2686,7 @@
         <v>45207</v>
       </c>
       <c r="B282" t="n">
-        <v>216.262691363634</v>
+        <v>218.1549899130658</v>
       </c>
     </row>
     <row r="283">
@@ -2694,7 +2694,7 @@
         <v>45208</v>
       </c>
       <c r="B283" t="n">
-        <v>216.6370498718794</v>
+        <v>218.5326240582584</v>
       </c>
     </row>
     <row r="284">
@@ -2702,7 +2702,7 @@
         <v>45209</v>
       </c>
       <c r="B284" t="n">
-        <v>217.0121613428412</v>
+        <v>218.911017754591</v>
       </c>
     </row>
     <row r="285">
@@ -2710,7 +2710,7 @@
         <v>45210</v>
       </c>
       <c r="B285" t="n">
-        <v>217.3879146228948</v>
+        <v>219.2900588758451</v>
       </c>
     </row>
     <row r="286">
@@ -2718,7 +2718,7 @@
         <v>45211</v>
       </c>
       <c r="B286" t="n">
-        <v>217.7641983682342</v>
+        <v>219.6696351039562</v>
       </c>
     </row>
     <row r="287">
@@ -2726,7 +2726,7 @@
         <v>45212</v>
       </c>
       <c r="B287" t="n">
-        <v>218.1409010778645</v>
+        <v>220.0496339622958</v>
       </c>
     </row>
     <row r="288">
@@ -2734,7 +2734,7 @@
         <v>45213</v>
       </c>
       <c r="B288" t="n">
-        <v>218.5179111266431</v>
+        <v>220.4299428490012</v>
       </c>
     </row>
     <row r="289">
@@ -2742,7 +2742,7 @@
         <v>45214</v>
       </c>
       <c r="B289" t="n">
-        <v>218.895116798356</v>
+        <v>220.8104490703416</v>
       </c>
     </row>
     <row r="290">
@@ -2750,7 +2750,7 @@
         <v>45215</v>
       </c>
       <c r="B290" t="n">
-        <v>219.2724063188218</v>
+        <v>221.1910398741115</v>
       </c>
     </row>
     <row r="291">
@@ -2758,7 +2758,7 @@
         <v>45216</v>
       </c>
       <c r="B291" t="n">
-        <v>219.6496678890131</v>
+        <v>221.571602483042</v>
       </c>
     </row>
     <row r="292">
@@ -2766,7 +2766,7 @@
         <v>45217</v>
       </c>
       <c r="B292" t="n">
-        <v>220.0267897181846</v>
+        <v>221.9520241282187</v>
       </c>
     </row>
     <row r="293">
@@ -2774,7 +2774,7 @@
         <v>45218</v>
       </c>
       <c r="B293" t="n">
-        <v>220.4036600569995</v>
+        <v>222.3321920824983</v>
       </c>
     </row>
     <row r="294">
@@ -2782,7 +2782,7 @@
         <v>45219</v>
       </c>
       <c r="B294" t="n">
-        <v>220.7801672306428</v>
+        <v>222.7119936939109</v>
       </c>
     </row>
     <row r="295">
@@ -2790,7 +2790,7 @@
         <v>45220</v>
       </c>
       <c r="B295" t="n">
-        <v>221.1561996719132</v>
+        <v>223.0913164190424</v>
       </c>
     </row>
     <row r="296">
@@ -2798,7 +2798,7 @@
         <v>45221</v>
       </c>
       <c r="B296" t="n">
-        <v>221.5316459542831</v>
+        <v>223.470047856383</v>
       </c>
     </row>
     <row r="297">
@@ -2806,7 +2806,7 @@
         <v>45222</v>
       </c>
       <c r="B297" t="n">
-        <v>221.9063948249159</v>
+        <v>223.8480757796339</v>
       </c>
     </row>
     <row r="298">
@@ -2814,7 +2814,7 @@
         <v>45223</v>
       </c>
       <c r="B298" t="n">
-        <v>222.2803352376338</v>
+        <v>224.2252881709631</v>
       </c>
     </row>
     <row r="299">
@@ -2822,7 +2822,7 @@
         <v>45224</v>
       </c>
       <c r="B299" t="n">
-        <v>222.6533563858221</v>
+        <v>224.6015732541981</v>
       </c>
     </row>
     <row r="300">
@@ -2830,7 +2830,7 @@
         <v>45225</v>
       </c>
       <c r="B300" t="n">
-        <v>223.0253477352642</v>
+        <v>224.9768195279477</v>
       </c>
     </row>
     <row r="301">
@@ -2838,7 +2838,7 @@
         <v>45226</v>
       </c>
       <c r="B301" t="n">
-        <v>223.3961990568949</v>
+        <v>225.3509157986427</v>
       </c>
     </row>
     <row r="302">
@@ -2846,7 +2846,7 @@
         <v>45227</v>
       </c>
       <c r="B302" t="n">
-        <v>223.7658004594641</v>
+        <v>225.7237512134844</v>
       </c>
     </row>
     <row r="303">
@@ -2854,7 +2854,7 @@
         <v>45228</v>
       </c>
       <c r="B303" t="n">
-        <v>224.1340424220995</v>
+        <v>226.0952152932928</v>
       </c>
     </row>
     <row r="304">
@@ -2862,7 +2862,7 @@
         <v>45229</v>
       </c>
       <c r="B304" t="n">
-        <v>224.5008158267602</v>
+        <v>226.4651979652444</v>
       </c>
     </row>
     <row r="305">
@@ -2870,7 +2870,7 @@
         <v>45230</v>
       </c>
       <c r="B305" t="n">
-        <v>224.866011990571</v>
+        <v>226.8335895954885</v>
       </c>
     </row>
     <row r="306">
@@ -2878,7 +2878,7 @@
         <v>45231</v>
       </c>
       <c r="B306" t="n">
-        <v>225.2295226980267</v>
+        <v>227.2002810216344</v>
       </c>
     </row>
     <row r="307">
@@ -2886,7 +2886,7 @@
         <v>45232</v>
       </c>
       <c r="B307" t="n">
-        <v>225.5912402330597</v>
+        <v>227.565163585099</v>
       </c>
     </row>
     <row r="308">
@@ -2894,7 +2894,7 @@
         <v>45233</v>
       </c>
       <c r="B308" t="n">
-        <v>225.9510574109577</v>
+        <v>227.9281291633036</v>
       </c>
     </row>
     <row r="309">
@@ -2902,7 +2902,7 @@
         <v>45234</v>
       </c>
       <c r="B309" t="n">
-        <v>226.3088676101256</v>
+        <v>228.2890702017142</v>
       </c>
     </row>
     <row r="310">
@@ -2910,7 +2910,7 @@
         <v>45235</v>
       </c>
       <c r="B310" t="n">
-        <v>226.664564803679</v>
+        <v>228.6478797457112</v>
       </c>
     </row>
     <row r="311">
@@ -2918,7 +2918,7 @@
         <v>45236</v>
       </c>
       <c r="B311" t="n">
-        <v>227.018043590863</v>
+        <v>229.0044514722831</v>
       </c>
     </row>
     <row r="312">
@@ -2926,7 +2926,7 @@
         <v>45237</v>
       </c>
       <c r="B312" t="n">
-        <v>227.3691992282843</v>
+        <v>229.3586797215318</v>
       </c>
     </row>
     <row r="313">
@@ -2934,7 +2934,7 @@
         <v>45238</v>
       </c>
       <c r="B313" t="n">
-        <v>227.7179276609487</v>
+        <v>229.710459527982</v>
       </c>
     </row>
     <row r="314">
@@ -2942,7 +2942,7 @@
         <v>45239</v>
       </c>
       <c r="B314" t="n">
-        <v>228.0641255530958</v>
+        <v>230.0596866516854</v>
       </c>
     </row>
     <row r="315">
@@ -2950,7 +2950,7 @@
         <v>45240</v>
       </c>
       <c r="B315" t="n">
-        <v>228.4076903188184</v>
+        <v>230.4062576091081</v>
       </c>
     </row>
     <row r="316">
@@ -2958,7 +2958,7 @@
         <v>45241</v>
       </c>
       <c r="B316" t="n">
-        <v>228.7485201524617</v>
+        <v>230.7500697037957</v>
       </c>
     </row>
     <row r="317">
@@ -2966,7 +2966,7 @@
         <v>45242</v>
       </c>
       <c r="B317" t="n">
-        <v>229.0865140587902</v>
+        <v>231.0910210568046</v>
       </c>
     </row>
     <row r="318">
@@ -2974,7 +2974,7 @@
         <v>45243</v>
       </c>
       <c r="B318" t="n">
-        <v>229.4215718829151</v>
+        <v>231.4290106368906</v>
       </c>
     </row>
     <row r="319">
@@ -2982,7 +2982,7 @@
         <v>45244</v>
       </c>
       <c r="B319" t="n">
-        <v>229.7535943399719</v>
+        <v>231.7639382904466</v>
       </c>
     </row>
     <row r="320">
@@ -2990,7 +2990,7 @@
         <v>45245</v>
       </c>
       <c r="B320" t="n">
-        <v>230.0824830445409</v>
+        <v>232.0957047711807</v>
       </c>
     </row>
     <row r="321">
@@ -2998,7 +2998,7 @@
         <v>45246</v>
       </c>
       <c r="B321" t="n">
-        <v>230.4081405398011</v>
+        <v>232.4242117695243</v>
       </c>
     </row>
     <row r="322">
@@ -3006,7 +3006,7 @@
         <v>45247</v>
       </c>
       <c r="B322" t="n">
-        <v>230.7304703264082</v>
+        <v>232.7493619417642</v>
       </c>
     </row>
     <row r="323">
@@ -3014,7 +3014,7 @@
         <v>45248</v>
       </c>
       <c r="B323" t="n">
-        <v>231.04937689109</v>
+        <v>233.071058938887</v>
       </c>
     </row>
     <row r="324">
@@ -3022,7 +3022,7 @@
         <v>45249</v>
       </c>
       <c r="B324" t="n">
-        <v>231.3647657349489</v>
+        <v>233.3892074351297</v>
       </c>
     </row>
     <row r="325">
@@ -3030,7 +3030,7 @@
         <v>45250</v>
       </c>
       <c r="B325" t="n">
-        <v>231.6765434014638</v>
+        <v>233.7037131562266</v>
       </c>
     </row>
     <row r="326">
@@ -3038,7 +3038,7 @@
         <v>45251</v>
       </c>
       <c r="B326" t="n">
-        <v>231.9846175041834</v>
+        <v>234.014482907345</v>
       </c>
     </row>
     <row r="327">
@@ -3046,7 +3046,7 @@
         <v>45252</v>
       </c>
       <c r="B327" t="n">
-        <v>232.2888967541022</v>
+        <v>234.3214246007006</v>
       </c>
     </row>
     <row r="328">
@@ -3054,7 +3054,7 @@
         <v>45253</v>
       </c>
       <c r="B328" t="n">
-        <v>232.5892909867117</v>
+        <v>234.6244472828455</v>
       </c>
     </row>
     <row r="329">
@@ -3062,7 +3062,7 @@
         <v>45254</v>
       </c>
       <c r="B329" t="n">
-        <v>232.8857111887177</v>
+        <v>234.923461161619</v>
       </c>
     </row>
     <row r="330">
@@ -3070,7 +3070,7 @@
         <v>45255</v>
       </c>
       <c r="B330" t="n">
-        <v>233.1780695244171</v>
+        <v>235.2183776327557</v>
       </c>
     </row>
     <row r="331">
@@ -3078,7 +3078,7 @@
         <v>45256</v>
       </c>
       <c r="B331" t="n">
-        <v>233.4662793617252</v>
+        <v>235.5091093061403</v>
       </c>
     </row>
     <row r="332">
@@ -3086,7 +3086,7 @@
         <v>45257</v>
       </c>
       <c r="B332" t="n">
-        <v>233.7502552978474</v>
+        <v>235.7955700317035</v>
       </c>
     </row>
     <row r="333">
@@ -3094,7 +3094,7 @@
         <v>45258</v>
       </c>
       <c r="B333" t="n">
-        <v>234.0299131845849</v>
+        <v>236.0776749249501</v>
       </c>
     </row>
     <row r="334">
@@ -3102,7 +3102,7 @@
         <v>45259</v>
       </c>
       <c r="B334" t="n">
-        <v>234.3051701532706</v>
+        <v>236.3553403921117</v>
       </c>
     </row>
     <row r="335">
@@ -3110,7 +3110,7 @@
         <v>45260</v>
       </c>
       <c r="B335" t="n">
-        <v>234.575944639324</v>
+        <v>236.6284841549181</v>
       </c>
     </row>
     <row r="336">
@@ -3118,7 +3118,7 @@
         <v>45261</v>
       </c>
       <c r="B336" t="n">
-        <v>234.8421564064211</v>
+        <v>236.8970252749772</v>
       </c>
     </row>
     <row r="337">
@@ -3126,7 +3126,7 @@
         <v>45262</v>
       </c>
       <c r="B337" t="n">
-        <v>235.1037265702699</v>
+        <v>237.1608841777598</v>
       </c>
     </row>
     <row r="338">
@@ -3134,7 +3134,7 @@
         <v>45263</v>
       </c>
       <c r="B338" t="n">
-        <v>235.3605776219859</v>
+        <v>237.4199826761783</v>
       </c>
     </row>
     <row r="339">
@@ -3142,7 +3142,7 @@
         <v>45264</v>
       </c>
       <c r="B339" t="n">
-        <v>235.612633451059</v>
+        <v>237.6742439937558</v>
       </c>
     </row>
     <row r="340">
@@ -3150,7 +3150,7 @@
         <v>45265</v>
       </c>
       <c r="B340" t="n">
-        <v>235.8598193679074</v>
+        <v>237.9235927873766</v>
       </c>
     </row>
     <row r="341">
@@ -3158,7 +3158,7 @@
         <v>45266</v>
       </c>
       <c r="B341" t="n">
-        <v>236.1020621260091</v>
+        <v>238.1679551696116</v>
       </c>
     </row>
     <row r="342">
@@ -3166,7 +3166,7 @@
         <v>45267</v>
       </c>
       <c r="B342" t="n">
-        <v>236.3392899436068</v>
+        <v>238.4072587306134</v>
       </c>
     </row>
     <row r="343">
@@ -3174,7 +3174,7 @@
         <v>45268</v>
       </c>
       <c r="B343" t="n">
-        <v>236.5714325249786</v>
+        <v>238.6414325595722</v>
       </c>
     </row>
     <row r="344">
@@ -3182,7 +3182,7 @@
         <v>45269</v>
       </c>
       <c r="B344" t="n">
-        <v>236.7984210812673</v>
+        <v>238.8704072657284</v>
       </c>
     </row>
     <row r="345">
@@ -3190,7 +3190,7 @@
         <v>45270</v>
       </c>
       <c r="B345" t="n">
-        <v>237.0201883508651</v>
+        <v>239.0941149989351</v>
       </c>
     </row>
     <row r="346">
@@ -3198,7 +3198,7 @@
         <v>45271</v>
       </c>
       <c r="B346" t="n">
-        <v>237.2366686193436</v>
+        <v>239.3124894697629</v>
       </c>
     </row>
     <row r="347">
@@ -3206,7 +3206,7 @@
         <v>45272</v>
       </c>
       <c r="B347" t="n">
-        <v>237.4477977389276</v>
+        <v>239.5254659691432</v>
       </c>
     </row>
     <row r="348">
@@ -3214,7 +3214,7 @@
         <v>45273</v>
       </c>
       <c r="B348" t="n">
-        <v>237.6535131475021</v>
+        <v>239.7329813875428</v>
       </c>
     </row>
     <row r="349">
@@ -3222,7 +3222,7 @@
         <v>45274</v>
       </c>
       <c r="B349" t="n">
-        <v>237.853753887152</v>
+        <v>239.9349742336645</v>
       </c>
     </row>
     <row r="350">
@@ -3230,7 +3230,7 @@
         <v>45275</v>
       </c>
       <c r="B350" t="n">
-        <v>238.0484606222245</v>
+        <v>240.131384652669</v>
       </c>
     </row>
     <row r="351">
@@ -3238,7 +3238,7 @@
         <v>45276</v>
       </c>
       <c r="B351" t="n">
-        <v>238.237575656912</v>
+        <v>240.32215444391</v>
       </c>
     </row>
     <row r="352">
@@ -3246,7 +3246,7 @@
         <v>45277</v>
       </c>
       <c r="B352" t="n">
-        <v>238.4210429523482</v>
+        <v>240.5072270781813</v>
       </c>
     </row>
     <row r="353">
@@ -3254,7 +3254,7 @@
         <v>45278</v>
       </c>
       <c r="B353" t="n">
-        <v>238.598808143214</v>
+        <v>240.6865477144671</v>
       </c>
     </row>
     <row r="354">
@@ -3262,7 +3262,7 @@
         <v>45279</v>
       </c>
       <c r="B354" t="n">
-        <v>238.7708185538467</v>
+        <v>240.8600632161929</v>
       </c>
     </row>
     <row r="355">
@@ -3270,7 +3270,7 @@
         <v>45280</v>
       </c>
       <c r="B355" t="n">
-        <v>238.9370232138495</v>
+        <v>241.0277221669707</v>
       </c>
     </row>
     <row r="356">
@@ -3278,7 +3278,7 @@
         <v>45281</v>
       </c>
       <c r="B356" t="n">
-        <v>239.0973728731946</v>
+        <v>241.189474885835</v>
       </c>
     </row>
     <row r="357">
@@ -3286,7 +3286,7 @@
         <v>45282</v>
       </c>
       <c r="B357" t="n">
-        <v>239.2518200168172</v>
+        <v>241.3452734419644</v>
       </c>
     </row>
     <row r="358">
@@ -3294,7 +3294,7 @@
         <v>45283</v>
       </c>
       <c r="B358" t="n">
-        <v>239.4003188786956</v>
+        <v>241.4950716688842</v>
       </c>
     </row>
     <row r="359">
@@ -3302,7 +3302,7 @@
         <v>45284</v>
       </c>
       <c r="B359" t="n">
-        <v>239.542825455412</v>
+        <v>241.6388251781469</v>
       </c>
     </row>
     <row r="360">
@@ -3310,7 +3310,7 @@
         <v>45285</v>
       </c>
       <c r="B360" t="n">
-        <v>239.6792975191923</v>
+        <v>241.7764913724852</v>
       </c>
     </row>
     <row r="361">
@@ -3318,7 +3318,7 @@
         <v>45286</v>
       </c>
       <c r="B361" t="n">
-        <v>239.8096946304185</v>
+        <v>241.9080294584347</v>
       </c>
     </row>
     <row r="362">
@@ -3326,7 +3326,7 @@
         <v>45287</v>
       </c>
       <c r="B362" t="n">
-        <v>239.9339781496126</v>
+        <v>242.0334004584217</v>
       </c>
     </row>
     <row r="363">
@@ -3334,7 +3334,7 @@
         <v>45288</v>
       </c>
       <c r="B363" t="n">
-        <v>240.0521112488854</v>
+        <v>242.1525672223131</v>
       </c>
     </row>
     <row r="364">
@@ -3342,7 +3342,7 @@
         <v>45289</v>
       </c>
       <c r="B364" t="n">
-        <v>240.1640589228502</v>
+        <v>242.2654944384251</v>
       </c>
     </row>
     <row r="365">
@@ -3350,7 +3350,7 @@
         <v>45290</v>
       </c>
       <c r="B365" t="n">
-        <v>240.269787998995</v>
+        <v>242.3721486439862</v>
       </c>
     </row>
     <row r="366">
@@ -3358,7 +3358,7 @@
         <v>45291</v>
       </c>
       <c r="B366" t="n">
-        <v>240.3692671475129</v>
+        <v>242.4724982350537</v>
       </c>
     </row>
   </sheetData>
